--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -1759,7 +1759,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F3 C4:F4 C5:F5 G3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:O5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,51 +30,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
-  <si>
-    <t>ID</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
   <si>
     <t>MapId</t>
   </si>
   <si>
+    <t>DropType</t>
+  </si>
+  <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
     <t>StartLevel</t>
   </si>
   <si>
     <t>EndLevel</t>
   </si>
   <si>
-    <t>ItemType</t>
-  </si>
-  <si>
-    <t>ItemId</t>
-  </si>
-  <si>
-    <t>ItemCount</t>
-  </si>
-  <si>
-    <t>ItemType1</t>
-  </si>
-  <si>
-    <t>ItemId1</t>
-  </si>
-  <si>
-    <t>ItemCount1</t>
-  </si>
-  <si>
-    <t>ItemType2</t>
-  </si>
-  <si>
-    <t>ItemId2</t>
-  </si>
-  <si>
-    <t>ItemCount2</t>
-  </si>
-  <si>
-    <t>Id</t>
+    <t>Max</t>
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>攻击宝石</t>
+  </si>
+  <si>
+    <t>防御宝石</t>
+  </si>
+  <si>
+    <t>生命宝石</t>
+  </si>
+  <si>
+    <t>命中宝石</t>
+  </si>
+  <si>
+    <t>闪避宝石</t>
+  </si>
+  <si>
+    <t>物理宝石</t>
+  </si>
+  <si>
+    <t>魔法宝石</t>
+  </si>
+  <si>
+    <t>道术宝石</t>
+  </si>
+  <si>
+    <t>增伤宝石</t>
+  </si>
+  <si>
+    <t>韧性宝石</t>
+  </si>
+  <si>
+    <t>盘古斧身</t>
+  </si>
+  <si>
+    <t>盘古斧背</t>
+  </si>
+  <si>
+    <t>盘古斧柄</t>
+  </si>
+  <si>
+    <t>盘古斧刃</t>
+  </si>
+  <si>
+    <t>盘古心核</t>
   </si>
 </sst>
 </file>
@@ -87,7 +123,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,17 +134,6 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -120,15 +145,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <color rgb="FFC00000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -601,153 +625,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1067,700 +1083,799 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
+  <dimension ref="C1:P55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="6" width="17.125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="14.125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14.125" style="4" customWidth="1"/>
-    <col min="11" max="12" width="14.5" style="4" customWidth="1"/>
-    <col min="13" max="13" width="14.125" style="3" customWidth="1"/>
-    <col min="14" max="15" width="14.5" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="1" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="9.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="11" width="11.125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23.125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="5" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="12:13">
+      <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="12:13">
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="I3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="K3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="6" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="H5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>60000001</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="5" t="s">
+      <c r="H6" s="2">
+        <v>50</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:15">
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="H7" s="2">
         <v>100</v>
       </c>
-      <c r="G6" s="7">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1">
-        <v>4001</v>
-      </c>
-      <c r="I6" s="7">
-        <v>20000</v>
-      </c>
-      <c r="J6" s="9">
-        <v>9</v>
-      </c>
-      <c r="K6" s="9">
-        <v>4003</v>
-      </c>
-      <c r="L6" s="9">
-        <v>70</v>
-      </c>
-      <c r="M6" s="7">
-        <v>5</v>
-      </c>
-      <c r="N6" s="7">
-        <v>4004</v>
-      </c>
-      <c r="O6" s="7">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:15">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <f>F6+1</f>
-        <v>101</v>
-      </c>
-      <c r="F7" s="1">
-        <v>200</v>
-      </c>
-      <c r="G7" s="7">
-        <v>5</v>
-      </c>
-      <c r="H7" s="1">
-        <v>4001</v>
-      </c>
-      <c r="I7" s="7">
-        <v>20000</v>
-      </c>
-      <c r="J7" s="9">
-        <v>9</v>
-      </c>
-      <c r="K7" s="9">
-        <v>4003</v>
-      </c>
-      <c r="L7" s="9">
-        <v>70</v>
-      </c>
-      <c r="M7" s="7">
-        <v>5</v>
-      </c>
-      <c r="N7" s="7">
-        <v>4004</v>
-      </c>
-      <c r="O7" s="7">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:15">
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
-        <f>F7+1</f>
-        <v>201</v>
-      </c>
-      <c r="F8" s="1">
-        <v>300</v>
-      </c>
-      <c r="G8" s="7">
-        <v>5</v>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="H8" s="1">
-        <v>4001</v>
-      </c>
-      <c r="I8" s="7">
-        <v>20000</v>
-      </c>
-      <c r="J8" s="9">
-        <v>9</v>
-      </c>
-      <c r="K8" s="9">
-        <v>4003</v>
-      </c>
-      <c r="L8" s="9">
-        <v>70</v>
-      </c>
-      <c r="M8" s="7">
-        <v>5</v>
-      </c>
-      <c r="N8" s="7">
-        <v>4004</v>
-      </c>
-      <c r="O8" s="7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:15">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:16">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
-        <f>F8+1</f>
-        <v>301</v>
-      </c>
-      <c r="F9" s="1">
-        <v>400</v>
-      </c>
-      <c r="G9" s="7">
-        <v>5</v>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>60000004</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="H9" s="1">
-        <v>4001</v>
-      </c>
-      <c r="I9" s="7">
-        <v>20000</v>
-      </c>
-      <c r="J9" s="9">
-        <v>9</v>
-      </c>
-      <c r="K9" s="9">
-        <v>4003</v>
-      </c>
-      <c r="L9" s="9">
-        <v>70</v>
-      </c>
-      <c r="M9" s="7">
-        <v>5</v>
-      </c>
-      <c r="N9" s="7">
-        <v>4004</v>
-      </c>
-      <c r="O9" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:15">
+        <v>10</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
-        <f>F9+1</f>
-        <v>401</v>
-      </c>
-      <c r="F10" s="1">
-        <v>500</v>
-      </c>
-      <c r="G10" s="7">
-        <v>5</v>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>60000005</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="H10" s="1">
-        <v>4001</v>
-      </c>
-      <c r="I10" s="7">
-        <v>20000</v>
-      </c>
-      <c r="J10" s="9">
+        <v>20</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>60000006</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="1">
+        <v>80</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="4"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>60000007</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="1">
+        <v>80</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="4"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>60000008</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="1">
+        <v>80</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="4"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="K10" s="9">
-        <v>4003</v>
-      </c>
-      <c r="L10" s="9">
-        <v>70</v>
-      </c>
-      <c r="M10" s="7">
-        <v>4</v>
-      </c>
-      <c r="N10" s="7">
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
+        <v>60000009</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="1">
+        <v>50</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="4"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4">
+        <v>60000010</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="1">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="4"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="4"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C17" s="2">
+        <v>11</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>61000001</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="7:15">
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-    </row>
-    <row r="12" customHeight="1" spans="7:15">
-      <c r="G12" s="7"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-    </row>
-    <row r="13" customHeight="1" spans="7:15">
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-    </row>
-    <row r="14" customHeight="1" spans="7:15">
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-    </row>
-    <row r="15" customHeight="1" spans="7:15">
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-    </row>
-    <row r="16" customHeight="1" spans="7:15">
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-    </row>
-    <row r="17" customHeight="1" spans="7:15">
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-    </row>
-    <row r="18" customHeight="1" spans="7:15">
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-    </row>
-    <row r="19" customHeight="1" spans="7:15">
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-    </row>
-    <row r="20" customHeight="1" spans="7:15">
-      <c r="G20" s="1"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-    </row>
-    <row r="21" customHeight="1" spans="7:15">
-      <c r="G21" s="1"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-    </row>
-    <row r="22" customHeight="1" spans="7:15">
-      <c r="G22" s="1"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-    </row>
-    <row r="23" customHeight="1" spans="7:15">
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2">
+        <v>100</v>
+      </c>
+      <c r="J17" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C18" s="1">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4">
+        <v>61000002</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2">
+        <v>100</v>
+      </c>
+      <c r="J18" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="4"/>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C19" s="2">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4">
+        <v>61000003</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2">
+        <v>100</v>
+      </c>
+      <c r="J19" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="4"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C20" s="2">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4">
+        <v>61000004</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2">
+        <v>100</v>
+      </c>
+      <c r="J20" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C21" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4">
+        <v>61000005</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2">
+        <v>100</v>
+      </c>
+      <c r="J21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O22" s="2"/>
+      <c r="P22" s="4"/>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-    </row>
-    <row r="24" customHeight="1" spans="7:15">
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-    </row>
-    <row r="25" customHeight="1" spans="7:15">
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-    </row>
-    <row r="27" customHeight="1" spans="7:15">
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-    </row>
-    <row r="28" customHeight="1" spans="7:15">
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-    </row>
-    <row r="29" customHeight="1" spans="7:15">
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-    </row>
-    <row r="30" customHeight="1" spans="9:15">
-      <c r="I30" s="7"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-    </row>
-    <row r="31" customHeight="1" spans="9:15">
-      <c r="I31" s="7"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-    </row>
-    <row r="32" customHeight="1" spans="9:15">
-      <c r="I32" s="7"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-    </row>
-    <row r="33" customHeight="1" spans="9:15">
-      <c r="I33" s="7"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-    </row>
-    <row r="34" customHeight="1" spans="9:15">
-      <c r="I34" s="7"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-    </row>
-    <row r="35" customHeight="1" spans="9:15">
-      <c r="I35" s="7"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-    </row>
-    <row r="36" customHeight="1" spans="9:15">
-      <c r="I36" s="7"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
-    </row>
-    <row r="37" customHeight="1" spans="9:15">
-      <c r="I37" s="7"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-    </row>
-    <row r="38" customHeight="1" spans="9:15">
-      <c r="I38" s="7"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
-    </row>
-    <row r="39" customHeight="1" spans="9:15">
-      <c r="I39" s="7"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
-    </row>
-    <row r="40" customHeight="1" spans="9:15">
-      <c r="I40" s="7"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-    </row>
-    <row r="41" customHeight="1" spans="9:15">
-      <c r="I41" s="7"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="N41" s="7"/>
-      <c r="O41" s="7"/>
-    </row>
-    <row r="42" customHeight="1" spans="9:15">
-      <c r="I42" s="7"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-    </row>
-    <row r="43" customHeight="1" spans="9:15">
-      <c r="I43" s="7"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="N43" s="7"/>
-      <c r="O43" s="7"/>
-    </row>
-    <row r="44" customHeight="1" spans="9:15">
-      <c r="I44" s="7"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="N44" s="7"/>
-      <c r="O44" s="7"/>
-    </row>
-    <row r="45" customHeight="1" spans="9:15">
-      <c r="I45" s="7"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="4"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O24" s="2"/>
+      <c r="P24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O25" s="2"/>
+      <c r="P25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O26" s="2"/>
+      <c r="P26" s="4"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O27" s="2"/>
+      <c r="P27" s="4"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O28" s="2"/>
+      <c r="P28" s="4"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O29" s="2"/>
+      <c r="P29" s="4"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O30" s="2"/>
+      <c r="P30" s="4"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O31" s="2"/>
+      <c r="P31" s="4"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O32" s="2"/>
+      <c r="P32" s="4"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O33" s="2"/>
+      <c r="P33" s="4"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O34" s="2"/>
+      <c r="P34" s="4"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O35" s="2"/>
+      <c r="P35" s="4"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O36" s="2"/>
+      <c r="P36" s="4"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O37" s="2"/>
+      <c r="P37" s="4"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O38" s="2"/>
+      <c r="P38" s="4"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O39" s="2"/>
+      <c r="P39" s="4"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O40" s="2"/>
+      <c r="P40" s="4"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O41" s="2"/>
+      <c r="P41" s="4"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O42" s="2"/>
+      <c r="P42" s="4"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O43" s="2"/>
+      <c r="P43" s="4"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O44" s="2"/>
+      <c r="P44" s="4"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O45" s="2"/>
+      <c r="P45" s="4"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O46" s="2"/>
+      <c r="P46" s="4"/>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O47" s="2"/>
+      <c r="P47" s="4"/>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O48" s="2"/>
+      <c r="P48" s="4"/>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O49" s="2"/>
+      <c r="P49" s="4"/>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O50" s="2"/>
+      <c r="P50" s="4"/>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O51" s="2"/>
+      <c r="P51" s="4"/>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O52" s="2"/>
+      <c r="P52" s="4"/>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O53" s="2"/>
+      <c r="P53" s="4"/>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O54" s="2"/>
+      <c r="P54" s="4"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O55" s="2"/>
+      <c r="P55" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:O5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G3 D4:G4 D5:G5 C4:C5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="26">
   <si>
     <t>#</t>
   </si>
@@ -50,25 +50,10 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>StartLevel</t>
-  </si>
-  <si>
-    <t>EndLevel</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>攻击宝石</t>
   </si>
   <si>
     <t>防御宝石</t>
@@ -77,10 +62,7 @@
     <t>生命宝石</t>
   </si>
   <si>
-    <t>命中宝石</t>
-  </si>
-  <si>
-    <t>闪避宝石</t>
+    <t>增伤宝石</t>
   </si>
   <si>
     <t>物理宝石</t>
@@ -92,25 +74,40 @@
     <t>道术宝石</t>
   </si>
   <si>
-    <t>增伤宝石</t>
+    <t>攻击宝石</t>
   </si>
   <si>
     <t>韧性宝石</t>
   </si>
   <si>
-    <t>盘古斧身</t>
+    <t>闪避宝石</t>
   </si>
   <si>
-    <t>盘古斧背</t>
+    <t>命中宝石</t>
   </si>
   <si>
-    <t>盘古斧柄</t>
+    <t>青龙神剑</t>
   </si>
   <si>
-    <t>盘古斧刃</t>
+    <t>青龙神甲</t>
   </si>
   <si>
-    <t>盘古心核</t>
+    <t>青龙面罩</t>
+  </si>
+  <si>
+    <t>青龙项链</t>
+  </si>
+  <si>
+    <t>青龙护腕</t>
+  </si>
+  <si>
+    <t>青龙护戒</t>
+  </si>
+  <si>
+    <t>青龙腰带</t>
+  </si>
+  <si>
+    <t>青龙战靴</t>
   </si>
 </sst>
 </file>
@@ -1083,35 +1080,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P55"/>
+  <dimension ref="C1:J145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="9.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="11" width="11.125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="23.125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="14.4166666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="12:13">
-      <c r="L1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="7:7">
+      <c r="G2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="12:13">
-      <c r="L2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:7">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1127,20 +1115,8 @@
       <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:7">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1156,83 +1132,45 @@
       <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="3" t="s">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="3" t="s">
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4">
-        <v>60000001</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="2">
-        <v>50</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="4"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1243,30 +1181,16 @@
         <v>1</v>
       </c>
       <c r="F7" s="4">
-        <v>60000002</v>
+        <v>60000003</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="2">
-        <v>100</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>9</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1277,30 +1201,16 @@
         <v>1</v>
       </c>
       <c r="F8" s="4">
-        <v>60000003</v>
+        <v>60000009</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="1">
-        <v>100</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="4"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:16">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1311,30 +1221,16 @@
         <v>1</v>
       </c>
       <c r="F9" s="4">
-        <v>60000004</v>
+        <v>60000002</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="1">
-        <v>10</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="4"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>8</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1345,30 +1241,16 @@
         <v>1</v>
       </c>
       <c r="F10" s="4">
-        <v>60000005</v>
+        <v>60000003</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="1">
-        <v>20</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="4"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1382,27 +1264,13 @@
         <v>60000006</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="1">
-        <v>80</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="4"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1416,27 +1284,13 @@
         <v>60000007</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="1">
-        <v>80</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="4"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>12</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1450,27 +1304,13 @@
         <v>60000008</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="1">
-        <v>80</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="4"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>13</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1481,30 +1321,16 @@
         <v>1</v>
       </c>
       <c r="F14" s="4">
-        <v>60000009</v>
+        <v>60000002</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="1">
-        <v>50</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="4"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+        <v>8</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1515,366 +1341,1562 @@
         <v>1</v>
       </c>
       <c r="F15" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4">
+        <v>60000001</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4">
         <v>60000010</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4">
+        <v>60000009</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4">
+        <v>60000006</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="H15" s="1">
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4">
+        <v>60000007</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
+        <v>60000008</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4">
+        <v>60000001</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4">
+        <v>60000010</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4">
+        <v>60000005</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="2"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
         <v>30</v>
       </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K15" s="2">
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
+        <v>60000009</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>60000006</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4">
+        <v>60000007</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="2">
+        <v>1</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
+        <v>60000008</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="2">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4">
+        <v>60000001</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="2">
+        <v>1</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="2">
+        <v>1</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I47" s="2"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C48" s="1">
+        <v>43</v>
+      </c>
+      <c r="D48" s="2">
+        <v>1</v>
+      </c>
+      <c r="E48" s="2">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4">
+        <v>60000010</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="2"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="2">
+        <v>1</v>
+      </c>
+      <c r="E49" s="2">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C50" s="1">
+        <v>45</v>
+      </c>
+      <c r="D50" s="2">
+        <v>1</v>
+      </c>
+      <c r="E50" s="2">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I50" s="2"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C51" s="1">
+        <v>46</v>
+      </c>
+      <c r="D51" s="2">
+        <v>1</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4">
+        <v>60000009</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I51" s="2"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C52" s="1">
+        <v>47</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="2"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C53" s="1">
+        <v>48</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C54" s="1">
+        <v>49</v>
+      </c>
+      <c r="D54" s="2">
+        <v>1</v>
+      </c>
+      <c r="E54" s="2">
+        <v>1</v>
+      </c>
+      <c r="F54" s="4">
+        <v>60000006</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="2">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4">
+        <v>60000007</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="2">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2">
+        <v>1</v>
+      </c>
+      <c r="F56" s="4">
+        <v>60000008</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="2">
+        <v>1</v>
+      </c>
+      <c r="E57" s="2">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="2"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C58" s="1">
+        <v>53</v>
+      </c>
+      <c r="D58" s="2">
+        <v>1</v>
+      </c>
+      <c r="E58" s="2">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C59" s="1">
+        <v>54</v>
+      </c>
+      <c r="D59" s="2">
+        <v>1</v>
+      </c>
+      <c r="E59" s="2">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4">
+        <v>60000001</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C60" s="1">
+        <v>55</v>
+      </c>
+      <c r="D60" s="2">
+        <v>1</v>
+      </c>
+      <c r="E60" s="2">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C61" s="1">
+        <v>56</v>
+      </c>
+      <c r="D61" s="2">
+        <v>1</v>
+      </c>
+      <c r="E61" s="2">
+        <v>1</v>
+      </c>
+      <c r="F61" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C62" s="1">
+        <v>57</v>
+      </c>
+      <c r="D62" s="2">
+        <v>1</v>
+      </c>
+      <c r="E62" s="2">
+        <v>1</v>
+      </c>
+      <c r="F62" s="4">
+        <v>60000010</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="2"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C63" s="1">
+        <v>58</v>
+      </c>
+      <c r="D63" s="2">
+        <v>1</v>
+      </c>
+      <c r="E63" s="2">
+        <v>1</v>
+      </c>
+      <c r="F63" s="4">
+        <v>60000005</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63" s="2"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C64" s="1">
+        <v>59</v>
+      </c>
+      <c r="D64" s="2">
+        <v>1</v>
+      </c>
+      <c r="E64" s="2">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4">
+        <v>60000004</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" s="2"/>
+      <c r="J64" s="4"/>
+    </row>
+    <row r="65" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="1"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="4"/>
+    </row>
+    <row r="66" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="1"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="4"/>
+    </row>
+    <row r="67" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C67" s="2">
         <v>1000</v>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="4"/>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="4"/>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C17" s="2">
-        <v>11</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2">
+      <c r="D67" s="2">
+        <v>1</v>
+      </c>
+      <c r="E67" s="2">
         <v>2</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F67" s="4">
         <v>61000001</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="2"/>
+      <c r="J67" s="4"/>
+    </row>
+    <row r="68" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C68" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D68" s="2">
+        <v>1</v>
+      </c>
+      <c r="E68" s="2">
+        <v>2</v>
+      </c>
+      <c r="F68" s="4">
+        <v>61000002</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I68" s="2"/>
+      <c r="J68" s="4"/>
+    </row>
+    <row r="69" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C69" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D69" s="2">
+        <v>1</v>
+      </c>
+      <c r="E69" s="2">
+        <v>2</v>
+      </c>
+      <c r="F69" s="4">
+        <v>61000003</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="4"/>
+    </row>
+    <row r="70" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C70" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D70" s="2">
+        <v>1</v>
+      </c>
+      <c r="E70" s="2">
+        <v>2</v>
+      </c>
+      <c r="F70" s="4">
+        <v>61000004</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="2"/>
+      <c r="J70" s="4"/>
+    </row>
+    <row r="71" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C71" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D71" s="2">
+        <v>1</v>
+      </c>
+      <c r="E71" s="2">
+        <v>2</v>
+      </c>
+      <c r="F71" s="4">
+        <v>61000005</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H17" s="2">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2">
-        <v>100</v>
-      </c>
-      <c r="J17" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K17" s="2">
-        <v>1</v>
-      </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C18" s="1">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="E18" s="2">
+      <c r="I71" s="2"/>
+      <c r="J71" s="4"/>
+    </row>
+    <row r="72" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C72" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D72" s="2">
+        <v>1</v>
+      </c>
+      <c r="E72" s="2">
         <v>2</v>
       </c>
-      <c r="F18" s="4">
-        <v>61000002</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="F72" s="4">
+        <v>61000006</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="2">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2">
-        <v>100</v>
-      </c>
-      <c r="J18" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="4"/>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C19" s="2">
-        <v>13</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1</v>
-      </c>
-      <c r="E19" s="2">
+      <c r="I72" s="2"/>
+      <c r="J72" s="4"/>
+    </row>
+    <row r="73" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C73" s="2">
+        <v>1006</v>
+      </c>
+      <c r="D73" s="2">
+        <v>1</v>
+      </c>
+      <c r="E73" s="2">
         <v>2</v>
       </c>
-      <c r="F19" s="4">
-        <v>61000003</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="F73" s="4">
+        <v>61000007</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="2">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2">
-        <v>100</v>
-      </c>
-      <c r="J19" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="4"/>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C20" s="2">
-        <v>14</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2">
+      <c r="I73" s="2"/>
+      <c r="J73" s="4"/>
+    </row>
+    <row r="74" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C74" s="2">
+        <v>1007</v>
+      </c>
+      <c r="D74" s="2">
+        <v>1</v>
+      </c>
+      <c r="E74" s="2">
         <v>2</v>
       </c>
-      <c r="F20" s="4">
-        <v>61000004</v>
-      </c>
-      <c r="G20" s="1" t="s">
+      <c r="F74" s="4">
+        <v>61000008</v>
+      </c>
+      <c r="G74" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="2">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2">
-        <v>100</v>
-      </c>
-      <c r="J20" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C21" s="1">
-        <v>15</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="2">
-        <v>2</v>
-      </c>
-      <c r="F21" s="4">
-        <v>61000005</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2">
-        <v>100</v>
-      </c>
-      <c r="J21" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K21" s="2">
-        <v>1</v>
-      </c>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O22" s="2"/>
-      <c r="P22" s="4"/>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="4"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O24" s="2"/>
-      <c r="P24" s="4"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O25" s="2"/>
-      <c r="P25" s="4"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O26" s="2"/>
-      <c r="P26" s="4"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O27" s="2"/>
-      <c r="P27" s="4"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O28" s="2"/>
-      <c r="P28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O29" s="2"/>
-      <c r="P29" s="4"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O30" s="2"/>
-      <c r="P30" s="4"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O31" s="2"/>
-      <c r="P31" s="4"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O32" s="2"/>
-      <c r="P32" s="4"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O33" s="2"/>
-      <c r="P33" s="4"/>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O34" s="2"/>
-      <c r="P34" s="4"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O35" s="2"/>
-      <c r="P35" s="4"/>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O36" s="2"/>
-      <c r="P36" s="4"/>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O37" s="2"/>
-      <c r="P37" s="4"/>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O38" s="2"/>
-      <c r="P38" s="4"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O39" s="2"/>
-      <c r="P39" s="4"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O40" s="2"/>
-      <c r="P40" s="4"/>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O41" s="2"/>
-      <c r="P41" s="4"/>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O42" s="2"/>
-      <c r="P42" s="4"/>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O43" s="2"/>
-      <c r="P43" s="4"/>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O44" s="2"/>
-      <c r="P44" s="4"/>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O45" s="2"/>
-      <c r="P45" s="4"/>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O46" s="2"/>
-      <c r="P46" s="4"/>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O47" s="2"/>
-      <c r="P47" s="4"/>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O48" s="2"/>
-      <c r="P48" s="4"/>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O49" s="2"/>
-      <c r="P49" s="4"/>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O50" s="2"/>
-      <c r="P50" s="4"/>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O51" s="2"/>
-      <c r="P51" s="4"/>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O52" s="2"/>
-      <c r="P52" s="4"/>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O53" s="2"/>
-      <c r="P53" s="4"/>
-    </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O54" s="2"/>
-      <c r="P54" s="4"/>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O55" s="2"/>
-      <c r="P55" s="4"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="4"/>
+    </row>
+    <row r="75" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="1"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="4"/>
+    </row>
+    <row r="76" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C76" s="1"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="1"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="4"/>
+    </row>
+    <row r="77" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C77" s="1"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="1"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="4"/>
+    </row>
+    <row r="78" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C78" s="1"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="5"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="4"/>
+    </row>
+    <row r="79" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C79" s="1"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="1"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="4"/>
+    </row>
+    <row r="80" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C80" s="1"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="1"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="4"/>
+    </row>
+    <row r="81" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="1"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="4"/>
+    </row>
+    <row r="82" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="1"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="4"/>
+    </row>
+    <row r="83" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="1"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="4"/>
+    </row>
+    <row r="84" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="1"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="4"/>
+    </row>
+    <row r="85" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="1"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="4"/>
+    </row>
+    <row r="86" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="1"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="4"/>
+    </row>
+    <row r="87" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="1"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="4"/>
+    </row>
+    <row r="88" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="1"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="4"/>
+    </row>
+    <row r="89" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="1"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="4"/>
+    </row>
+    <row r="90" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="1"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="4"/>
+    </row>
+    <row r="91" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C91" s="1"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="1"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="4"/>
+    </row>
+    <row r="92" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C92" s="1"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="1"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="4"/>
+    </row>
+    <row r="93" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C93" s="1"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="5"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="4"/>
+    </row>
+    <row r="94" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C94" s="1"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="1"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="4"/>
+    </row>
+    <row r="95" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C95" s="1"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="4"/>
+    </row>
+    <row r="96" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="1"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="4"/>
+    </row>
+    <row r="97" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="1"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="4"/>
+    </row>
+    <row r="98" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="1"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="4"/>
+    </row>
+    <row r="99" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="1"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="4"/>
+    </row>
+    <row r="100" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="1"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="4"/>
+    </row>
+    <row r="101" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="1"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="4"/>
+    </row>
+    <row r="102" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="1"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="4"/>
+    </row>
+    <row r="103" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="1"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="4"/>
+    </row>
+    <row r="104" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="1"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="4"/>
+    </row>
+    <row r="105" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="1"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="4"/>
+    </row>
+    <row r="106" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="1"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="4"/>
+    </row>
+    <row r="107" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C107" s="1"/>
+      <c r="J107" s="4"/>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I108" s="2"/>
+      <c r="J108" s="4"/>
+    </row>
+    <row r="109" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C109" s="1"/>
+      <c r="J109" s="4"/>
+    </row>
+    <row r="110" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C110" s="1"/>
+      <c r="J110" s="4"/>
+    </row>
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I111" s="2"/>
+      <c r="J111" s="4"/>
+    </row>
+    <row r="112" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I112" s="2"/>
+      <c r="J112" s="4"/>
+    </row>
+    <row r="113" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="4"/>
+    </row>
+    <row r="114" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I114" s="2"/>
+      <c r="J114" s="4"/>
+    </row>
+    <row r="115" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I115" s="2"/>
+      <c r="J115" s="4"/>
+    </row>
+    <row r="116" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I116" s="2"/>
+      <c r="J116" s="4"/>
+    </row>
+    <row r="117" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I117" s="2"/>
+      <c r="J117" s="4"/>
+    </row>
+    <row r="118" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I118" s="2"/>
+      <c r="J118" s="4"/>
+    </row>
+    <row r="119" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I119" s="2"/>
+      <c r="J119" s="4"/>
+    </row>
+    <row r="120" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I120" s="2"/>
+      <c r="J120" s="4"/>
+    </row>
+    <row r="121" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I121" s="2"/>
+      <c r="J121" s="4"/>
+    </row>
+    <row r="122" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I122" s="2"/>
+      <c r="J122" s="4"/>
+    </row>
+    <row r="123" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I123" s="2"/>
+      <c r="J123" s="4"/>
+    </row>
+    <row r="124" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I124" s="2"/>
+      <c r="J124" s="4"/>
+    </row>
+    <row r="125" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I125" s="2"/>
+      <c r="J125" s="4"/>
+    </row>
+    <row r="126" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I126" s="2"/>
+      <c r="J126" s="4"/>
+    </row>
+    <row r="127" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I127" s="2"/>
+      <c r="J127" s="4"/>
+    </row>
+    <row r="128" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I128" s="2"/>
+      <c r="J128" s="4"/>
+    </row>
+    <row r="129" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I129" s="2"/>
+      <c r="J129" s="4"/>
+    </row>
+    <row r="130" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I130" s="2"/>
+      <c r="J130" s="4"/>
+    </row>
+    <row r="131" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I131" s="2"/>
+      <c r="J131" s="4"/>
+    </row>
+    <row r="132" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I132" s="2"/>
+      <c r="J132" s="4"/>
+    </row>
+    <row r="133" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I133" s="2"/>
+      <c r="J133" s="4"/>
+    </row>
+    <row r="134" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I134" s="2"/>
+      <c r="J134" s="4"/>
+    </row>
+    <row r="135" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I135" s="2"/>
+      <c r="J135" s="4"/>
+    </row>
+    <row r="136" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I136" s="2"/>
+      <c r="J136" s="4"/>
+    </row>
+    <row r="137" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I137" s="2"/>
+      <c r="J137" s="4"/>
+    </row>
+    <row r="138" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I138" s="2"/>
+      <c r="J138" s="4"/>
+    </row>
+    <row r="139" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I139" s="2"/>
+      <c r="J139" s="4"/>
+    </row>
+    <row r="140" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I140" s="2"/>
+      <c r="J140" s="4"/>
+    </row>
+    <row r="141" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I141" s="2"/>
+      <c r="J141" s="4"/>
+    </row>
+    <row r="142" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I142" s="2"/>
+      <c r="J142" s="4"/>
+    </row>
+    <row r="143" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I143" s="2"/>
+      <c r="J143" s="4"/>
+    </row>
+    <row r="144" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I144" s="2"/>
+      <c r="J144" s="4"/>
+    </row>
+    <row r="145" s="1" customFormat="1" customHeight="1" spans="9:10">
+      <c r="I145" s="2"/>
+      <c r="J145" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G3 D4:G4 D5:G5 C4:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
   <si>
     <t>#</t>
   </si>
@@ -75,9 +75,6 @@
     <t>MapId</t>
   </si>
   <si>
-    <t>DropType</t>
-  </si>
-  <si>
     <t>ItemId</t>
   </si>
   <si>
@@ -93,6 +90,12 @@
     <t>RateLevel</t>
   </si>
   <si>
+    <t>ExcludeStart</t>
+  </si>
+  <si>
+    <t>ExcludeLevel</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -130,6 +133,9 @@
   </si>
   <si>
     <t>韧性宝石</t>
+  </si>
+  <si>
+    <t>青龙精华</t>
   </si>
   <si>
     <t>青龙神剑</t>
@@ -344,12 +350,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1137,26 +1143,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N96"/>
+  <dimension ref="C1:O96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="5" width="9" style="1"/>
-    <col min="6" max="10" width="14.4166666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.25" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="11" width="14.4159292035398" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.2477876106195" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="11:11">
-      <c r="K1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="12:12">
+      <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="11:11">
-      <c r="K2" s="1" t="s">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="12:12">
+      <c r="L2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1184,8 +1190,11 @@
       <c r="K3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1213,1199 +1222,1312 @@
       <c r="K4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="L5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="E6" s="4">
         <v>60000001</v>
       </c>
-      <c r="G6" s="1">
+      <c r="F6" s="1">
         <v>4</v>
       </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="G6" s="4">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
         <v>10000</v>
       </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
       <c r="J6" s="4">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="K6" s="4">
+        <v>10</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M6" s="2"/>
-      <c r="N6" s="4"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N6" s="2"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="E7" s="4">
         <v>60000002</v>
       </c>
-      <c r="G7" s="1">
+      <c r="F7" s="1">
         <v>10</v>
       </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="G7" s="4">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
         <v>10000</v>
       </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
       <c r="J7" s="4">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L7" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="K7" s="4">
+        <v>10</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N7" s="2"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="E8" s="4">
         <v>60000003</v>
       </c>
-      <c r="G8" s="1">
+      <c r="F8" s="1">
         <v>20</v>
       </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
+      <c r="G8" s="4">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
         <v>10000</v>
       </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
       <c r="J8" s="4">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="4"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
+        <v>50</v>
+      </c>
+      <c r="K8" s="4">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:15">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E9" s="4">
         <v>60000004</v>
       </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
         <v>200</v>
       </c>
-      <c r="I9" s="1">
+      <c r="H9" s="1">
         <v>10000</v>
       </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
       <c r="J9" s="4">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="1"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="4"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>50</v>
+      </c>
+      <c r="K9" s="4">
+        <v>10</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="E10" s="4">
         <v>60000005</v>
       </c>
-      <c r="G10" s="1">
+      <c r="F10" s="1">
         <v>2</v>
       </c>
-      <c r="H10" s="4">
+      <c r="G10" s="4">
         <v>100</v>
       </c>
-      <c r="I10" s="1">
+      <c r="H10" s="1">
         <v>10000</v>
       </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
       <c r="J10" s="4">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="4"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>50</v>
+      </c>
+      <c r="K10" s="4">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="E11" s="4">
         <v>60000006</v>
       </c>
-      <c r="G11" s="1">
+      <c r="F11" s="1">
         <v>6</v>
       </c>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
         <v>10000</v>
       </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
       <c r="J11" s="4">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="4"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>50</v>
+      </c>
+      <c r="K11" s="4">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
       </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4">
+      <c r="E12" s="4">
         <v>60000007</v>
       </c>
-      <c r="G12" s="1">
+      <c r="F12" s="1">
         <v>6</v>
       </c>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
         <v>10000</v>
       </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
       <c r="J12" s="4">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L12" s="1"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="4"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>50</v>
+      </c>
+      <c r="K12" s="4">
+        <v>10</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
       </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="E13" s="4">
         <v>60000008</v>
       </c>
-      <c r="G13" s="1">
+      <c r="F13" s="1">
         <v>6</v>
       </c>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1">
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
         <v>10000</v>
       </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
       <c r="J13" s="4">
-        <v>1</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="4"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>50</v>
+      </c>
+      <c r="K13" s="4">
+        <v>10</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="E14" s="4">
         <v>60000009</v>
       </c>
-      <c r="G14" s="1">
+      <c r="F14" s="1">
         <v>5</v>
       </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1">
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
         <v>10000</v>
       </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
       <c r="J14" s="4">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="4"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>50</v>
+      </c>
+      <c r="K14" s="4">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="1"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
       </c>
-      <c r="E15" s="2">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="E15" s="4">
         <v>60000010</v>
       </c>
-      <c r="G15" s="1">
+      <c r="F15" s="1">
         <v>3</v>
       </c>
-      <c r="H15" s="4">
+      <c r="G15" s="4">
         <v>300</v>
       </c>
-      <c r="I15" s="1">
+      <c r="H15" s="1">
         <v>10000</v>
       </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
       <c r="J15" s="4">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="1"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="4"/>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="3:14">
+        <v>50</v>
+      </c>
+      <c r="K15" s="4">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="1"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="3:15">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="1"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="4"/>
-    </row>
-    <row r="17" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="1"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="4"/>
-    </row>
-    <row r="18" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K16" s="4"/>
+      <c r="L16" s="1"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C17" s="1">
+        <v>999</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>4028</v>
+      </c>
+      <c r="F17" s="4">
+        <v>70</v>
+      </c>
+      <c r="G17" s="4">
+        <v>50</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I17" s="4">
+        <v>10</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" customFormat="1" customHeight="1" spans="3:15">
       <c r="C18" s="2">
         <v>1000</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
       </c>
-      <c r="E18" s="2">
-        <v>2</v>
+      <c r="E18" s="4">
+        <v>61000001</v>
       </c>
       <c r="F18" s="4">
-        <v>61000001</v>
+        <v>3</v>
       </c>
       <c r="G18" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H18" s="4">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="I18" s="4">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="J18" s="4">
-        <v>10</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="4"/>
-    </row>
-    <row r="19" customFormat="1" customHeight="1" spans="3:14">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" customFormat="1" customHeight="1" spans="3:15">
       <c r="C19" s="2">
         <v>1001</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="E19" s="2">
-        <v>2</v>
+      <c r="E19" s="4">
+        <v>61000002</v>
       </c>
       <c r="F19" s="4">
-        <v>61000002</v>
+        <v>3</v>
       </c>
       <c r="G19" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H19" s="4">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="I19" s="4">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="J19" s="4">
-        <v>10</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="4"/>
-    </row>
-    <row r="20" customFormat="1" customHeight="1" spans="3:14">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" customFormat="1" customHeight="1" spans="3:15">
       <c r="C20" s="2">
         <v>1002</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
       </c>
-      <c r="E20" s="2">
-        <v>2</v>
+      <c r="E20" s="4">
+        <v>61000003</v>
       </c>
       <c r="F20" s="4">
-        <v>61000003</v>
+        <v>3</v>
       </c>
       <c r="G20" s="4">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="H20" s="4">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="I20" s="4">
-        <v>450</v>
+        <v>10</v>
       </c>
       <c r="J20" s="4">
-        <v>10</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="4"/>
-    </row>
-    <row r="21" customFormat="1" customHeight="1" spans="3:14">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" customFormat="1" customHeight="1" spans="3:15">
       <c r="C21" s="2">
         <v>1003</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
       </c>
-      <c r="E21" s="2">
-        <v>2</v>
+      <c r="E21" s="4">
+        <v>61000004</v>
       </c>
       <c r="F21" s="4">
-        <v>61000004</v>
+        <v>3</v>
       </c>
       <c r="G21" s="4">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="H21" s="4">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="I21" s="4">
-        <v>450</v>
+        <v>10</v>
       </c>
       <c r="J21" s="4">
-        <v>10</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="4"/>
-    </row>
-    <row r="22" customFormat="1" customHeight="1" spans="3:14">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" customFormat="1" customHeight="1" spans="3:15">
       <c r="C22" s="2">
         <v>1004</v>
       </c>
       <c r="D22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="4">
+        <v>61000005</v>
+      </c>
+      <c r="F22" s="4">
         <v>2</v>
       </c>
-      <c r="F22" s="4">
-        <v>61000005</v>
-      </c>
       <c r="G22" s="4">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="H22" s="4">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="I22" s="4">
-        <v>650</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4">
-        <v>10</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" s="2"/>
-      <c r="N22" s="4"/>
-    </row>
-    <row r="23" customFormat="1" customHeight="1" spans="3:14">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" customFormat="1" customHeight="1" spans="3:15">
       <c r="C23" s="2">
         <v>1005</v>
       </c>
       <c r="D23" s="2">
         <v>1</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="4">
+        <v>61000006</v>
+      </c>
+      <c r="F23" s="4">
         <v>2</v>
       </c>
-      <c r="F23" s="4">
-        <v>61000006</v>
-      </c>
       <c r="G23" s="4">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="H23" s="4">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="I23" s="4">
-        <v>650</v>
+        <v>10</v>
       </c>
       <c r="J23" s="4">
-        <v>10</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="4"/>
-    </row>
-    <row r="24" customFormat="1" customHeight="1" spans="3:14">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" customFormat="1" customHeight="1" spans="3:15">
       <c r="C24" s="2">
         <v>1006</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="4">
+        <v>61000007</v>
+      </c>
+      <c r="F24" s="4">
         <v>2</v>
       </c>
-      <c r="F24" s="4">
-        <v>61000007</v>
-      </c>
       <c r="G24" s="4">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="H24" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="I24" s="4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="J24" s="4">
-        <v>10</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="4"/>
-    </row>
-    <row r="25" customFormat="1" customHeight="1" spans="3:14">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="3:15">
       <c r="C25" s="2">
         <v>1007</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="4">
+        <v>61000008</v>
+      </c>
+      <c r="F25" s="4">
         <v>2</v>
       </c>
-      <c r="F25" s="4">
-        <v>61000008</v>
-      </c>
       <c r="G25" s="4">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="H25" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="I25" s="4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4">
-        <v>10</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M25" s="2"/>
-      <c r="N25" s="4"/>
-    </row>
-    <row r="26" customFormat="1" customHeight="1" spans="3:14">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="3:15">
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
-      <c r="K26" s="1"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="4"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K26" s="4"/>
+      <c r="L26" s="1"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="3:15">
       <c r="C27" s="1"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+      <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-      <c r="K27" s="1"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="4"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K27" s="4"/>
+      <c r="L27" s="1"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="4"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="3:15">
       <c r="C28" s="1"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-      <c r="K28" s="1"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="4"/>
-    </row>
-    <row r="29" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K28" s="4"/>
+      <c r="L28" s="1"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="4"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="3:15">
       <c r="C29" s="1"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-      <c r="K29" s="5"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="4"/>
-    </row>
-    <row r="30" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="3:15">
       <c r="C30" s="1"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
+      <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-      <c r="K30" s="1"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="4"/>
-    </row>
-    <row r="31" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K30" s="4"/>
+      <c r="L30" s="1"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="3:15">
       <c r="C31" s="1"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+      <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
-      <c r="K31" s="1"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="4"/>
-    </row>
-    <row r="32" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K31" s="4"/>
+      <c r="L31" s="1"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="3:15">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
-      <c r="K32" s="1"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="4"/>
-    </row>
-    <row r="33" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K32" s="4"/>
+      <c r="L32" s="1"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:15">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="1"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="4"/>
-    </row>
-    <row r="34" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K33" s="4"/>
+      <c r="L33" s="1"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="3:15">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+      <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
-      <c r="K34" s="1"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="4"/>
-    </row>
-    <row r="35" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K34" s="4"/>
+      <c r="L34" s="1"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="3:15">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
-      <c r="K35" s="1"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="4"/>
-    </row>
-    <row r="36" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K35" s="4"/>
+      <c r="L35" s="1"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="4"/>
+    </row>
+    <row r="36" customFormat="1" customHeight="1" spans="3:15">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
-      <c r="K36" s="1"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="4"/>
-    </row>
-    <row r="37" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K36" s="4"/>
+      <c r="L36" s="1"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" customFormat="1" customHeight="1" spans="3:15">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
-      <c r="K37" s="1"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="4"/>
-    </row>
-    <row r="38" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K37" s="4"/>
+      <c r="L37" s="1"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" customFormat="1" customHeight="1" spans="3:15">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
-      <c r="K38" s="1"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="4"/>
-    </row>
-    <row r="39" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K38" s="4"/>
+      <c r="L38" s="1"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="3:15">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
-      <c r="K39" s="1"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="4"/>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K39" s="4"/>
+      <c r="L39" s="1"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="4"/>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:15">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-      <c r="K40" s="1"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="4"/>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K40" s="4"/>
+      <c r="L40" s="1"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="4"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="3:15">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
-      <c r="K41" s="1"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="4"/>
-    </row>
-    <row r="42" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K41" s="4"/>
+      <c r="L41" s="1"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="3:15">
       <c r="C42" s="1"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+      <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
-      <c r="K42" s="1"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="4"/>
-    </row>
-    <row r="43" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K42" s="4"/>
+      <c r="L42" s="1"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="3:15">
       <c r="C43" s="1"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+      <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
-      <c r="K43" s="1"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="4"/>
-    </row>
-    <row r="44" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K43" s="4"/>
+      <c r="L43" s="1"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="4"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="3:15">
       <c r="C44" s="1"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
+      <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
-      <c r="K44" s="5"/>
-      <c r="M44" s="2"/>
-      <c r="N44" s="4"/>
-    </row>
-    <row r="45" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K44" s="4"/>
+      <c r="L44" s="5"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="3:15">
       <c r="C45" s="1"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
+      <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
-      <c r="K45" s="1"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="4"/>
-    </row>
-    <row r="46" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K45" s="4"/>
+      <c r="L45" s="1"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="4"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="3:15">
       <c r="C46" s="1"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="4"/>
-    </row>
-    <row r="47" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N46" s="2"/>
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="3:15">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+      <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
-      <c r="K47" s="1"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="4"/>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K47" s="4"/>
+      <c r="L47" s="1"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="3:15">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+      <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
-      <c r="K48" s="1"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="4"/>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K48" s="4"/>
+      <c r="L48" s="1"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="4"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:15">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+      <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
-      <c r="K49" s="1"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="4"/>
-    </row>
-    <row r="50" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K49" s="4"/>
+      <c r="L49" s="1"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="4"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:15">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
-      <c r="K50" s="1"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="4"/>
-    </row>
-    <row r="51" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K50" s="4"/>
+      <c r="L50" s="1"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="4"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:15">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
+      <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
-      <c r="K51" s="1"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="4"/>
-    </row>
-    <row r="52" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K51" s="4"/>
+      <c r="L51" s="1"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="4"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:15">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
+      <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
-      <c r="K52" s="1"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="4"/>
-    </row>
-    <row r="53" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K52" s="4"/>
+      <c r="L52" s="1"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="4"/>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="3:15">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
+      <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
-      <c r="K53" s="1"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="4"/>
-    </row>
-    <row r="54" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K53" s="4"/>
+      <c r="L53" s="1"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="4"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="3:15">
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
+      <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
-      <c r="K54" s="1"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="4"/>
-    </row>
-    <row r="55" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K54" s="4"/>
+      <c r="L54" s="1"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="4"/>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="3:15">
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
+      <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
-      <c r="K55" s="1"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="4"/>
-    </row>
-    <row r="56" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K55" s="4"/>
+      <c r="L55" s="1"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="4"/>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="3:15">
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
+      <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
-      <c r="K56" s="1"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="4"/>
-    </row>
-    <row r="57" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K56" s="4"/>
+      <c r="L56" s="1"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="4"/>
+    </row>
+    <row r="57" customFormat="1" customHeight="1" spans="3:15">
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
+      <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
-      <c r="K57" s="1"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="4"/>
-    </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="K57" s="4"/>
+      <c r="L57" s="1"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="4"/>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C58" s="1"/>
-      <c r="N58" s="4"/>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M59" s="2"/>
-      <c r="N59" s="4"/>
-    </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O58" s="4"/>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N59" s="2"/>
+      <c r="O59" s="4"/>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C60" s="1"/>
-      <c r="N60" s="4"/>
-    </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O60" s="4"/>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C61" s="1"/>
-      <c r="N61" s="4"/>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M62" s="2"/>
-      <c r="N62" s="4"/>
-    </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M63" s="2"/>
-      <c r="N63" s="4"/>
-    </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O61" s="4"/>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N62" s="2"/>
+      <c r="O62" s="4"/>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N63" s="2"/>
+      <c r="O63" s="4"/>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="2"/>
-      <c r="N64" s="4"/>
-    </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M65" s="2"/>
-      <c r="N65" s="4"/>
-    </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M66" s="2"/>
-      <c r="N66" s="4"/>
-    </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M67" s="2"/>
-      <c r="N67" s="4"/>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M68" s="2"/>
-      <c r="N68" s="4"/>
-    </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M69" s="2"/>
-      <c r="N69" s="4"/>
-    </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M70" s="2"/>
-      <c r="N70" s="4"/>
-    </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M71" s="2"/>
-      <c r="N71" s="4"/>
-    </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M72" s="2"/>
-      <c r="N72" s="4"/>
-    </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M73" s="2"/>
-      <c r="N73" s="4"/>
-    </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M74" s="2"/>
-      <c r="N74" s="4"/>
-    </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M75" s="2"/>
-      <c r="N75" s="4"/>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M76" s="2"/>
-      <c r="N76" s="4"/>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M77" s="2"/>
-      <c r="N77" s="4"/>
-    </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M78" s="2"/>
-      <c r="N78" s="4"/>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M79" s="2"/>
-      <c r="N79" s="4"/>
-    </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M80" s="2"/>
-      <c r="N80" s="4"/>
-    </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M81" s="2"/>
-      <c r="N81" s="4"/>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M82" s="2"/>
-      <c r="N82" s="4"/>
-    </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M83" s="2"/>
-      <c r="N83" s="4"/>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M84" s="2"/>
-      <c r="N84" s="4"/>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M85" s="2"/>
-      <c r="N85" s="4"/>
-    </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M86" s="2"/>
-      <c r="N86" s="4"/>
-    </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M87" s="2"/>
-      <c r="N87" s="4"/>
-    </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M88" s="2"/>
-      <c r="N88" s="4"/>
-    </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M89" s="2"/>
-      <c r="N89" s="4"/>
-    </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M90" s="2"/>
-      <c r="N90" s="4"/>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M91" s="2"/>
-      <c r="N91" s="4"/>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M92" s="2"/>
-      <c r="N92" s="4"/>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M93" s="2"/>
-      <c r="N93" s="4"/>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M94" s="2"/>
-      <c r="N94" s="4"/>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M95" s="2"/>
-      <c r="N95" s="4"/>
-    </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="13:14">
-      <c r="M96" s="2"/>
-      <c r="N96" s="4"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="4"/>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N65" s="2"/>
+      <c r="O65" s="4"/>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N66" s="2"/>
+      <c r="O66" s="4"/>
+    </row>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N67" s="2"/>
+      <c r="O67" s="4"/>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N68" s="2"/>
+      <c r="O68" s="4"/>
+    </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N69" s="2"/>
+      <c r="O69" s="4"/>
+    </row>
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N70" s="2"/>
+      <c r="O70" s="4"/>
+    </row>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N71" s="2"/>
+      <c r="O71" s="4"/>
+    </row>
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N72" s="2"/>
+      <c r="O72" s="4"/>
+    </row>
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N73" s="2"/>
+      <c r="O73" s="4"/>
+    </row>
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N74" s="2"/>
+      <c r="O74" s="4"/>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N75" s="2"/>
+      <c r="O75" s="4"/>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N76" s="2"/>
+      <c r="O76" s="4"/>
+    </row>
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N77" s="2"/>
+      <c r="O77" s="4"/>
+    </row>
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N78" s="2"/>
+      <c r="O78" s="4"/>
+    </row>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N79" s="2"/>
+      <c r="O79" s="4"/>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N80" s="2"/>
+      <c r="O80" s="4"/>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N81" s="2"/>
+      <c r="O81" s="4"/>
+    </row>
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N82" s="2"/>
+      <c r="O82" s="4"/>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N83" s="2"/>
+      <c r="O83" s="4"/>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N84" s="2"/>
+      <c r="O84" s="4"/>
+    </row>
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N85" s="2"/>
+      <c r="O85" s="4"/>
+    </row>
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N86" s="2"/>
+      <c r="O86" s="4"/>
+    </row>
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N87" s="2"/>
+      <c r="O87" s="4"/>
+    </row>
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N88" s="2"/>
+      <c r="O88" s="4"/>
+    </row>
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N89" s="2"/>
+      <c r="O89" s="4"/>
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N90" s="2"/>
+      <c r="O90" s="4"/>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N91" s="2"/>
+      <c r="O91" s="4"/>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N92" s="2"/>
+      <c r="O92" s="4"/>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N93" s="2"/>
+      <c r="O93" s="4"/>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N94" s="2"/>
+      <c r="O94" s="4"/>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N95" s="2"/>
+      <c r="O95" s="4"/>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N96" s="2"/>
+      <c r="O96" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:K5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:E5 L3:L5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -160,6 +160,33 @@
   </si>
   <si>
     <t>青龙战靴</t>
+  </si>
+  <si>
+    <t>白虎精华</t>
+  </si>
+  <si>
+    <t>白虎神剑</t>
+  </si>
+  <si>
+    <t>白虎神甲</t>
+  </si>
+  <si>
+    <t>白虎面罩</t>
+  </si>
+  <si>
+    <t>白虎项链</t>
+  </si>
+  <si>
+    <t>白虎护腕</t>
+  </si>
+  <si>
+    <t>白虎护戒</t>
+  </si>
+  <si>
+    <t>白虎腰带</t>
+  </si>
+  <si>
+    <t>白虎战靴</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4">
         <v>60000001</v>
@@ -1298,7 +1325,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4">
         <v>60000002</v>
@@ -1333,7 +1360,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4">
         <v>60000003</v>
@@ -1368,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="4">
         <v>60000004</v>
@@ -1403,7 +1430,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4">
         <v>60000005</v>
@@ -1438,7 +1465,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4">
         <v>60000006</v>
@@ -1473,7 +1500,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4">
         <v>60000007</v>
@@ -1508,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="4">
         <v>60000008</v>
@@ -1543,7 +1570,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="4">
         <v>60000009</v>
@@ -1578,7 +1605,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="4">
         <v>60000010</v>
@@ -1943,128 +1970,308 @@
       <c r="O26" s="4"/>
     </row>
     <row r="27" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C27" s="1"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="C27" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="4">
+        <v>4029</v>
+      </c>
+      <c r="F27" s="4">
+        <v>70</v>
+      </c>
+      <c r="G27" s="4">
+        <v>50</v>
+      </c>
+      <c r="H27" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I27" s="4">
+        <v>10</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" s="4"/>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C28" s="1"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="C28" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="4">
+        <v>61000009</v>
+      </c>
+      <c r="F28" s="4">
+        <v>3</v>
+      </c>
+      <c r="G28" s="4">
+        <v>50</v>
+      </c>
+      <c r="H28" s="4">
+        <v>400</v>
+      </c>
+      <c r="I28" s="4">
+        <v>10</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="N28" s="2"/>
       <c r="O28" s="4"/>
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C29" s="1"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="5"/>
+      <c r="C29" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="4">
+        <v>61000010</v>
+      </c>
+      <c r="F29" s="4">
+        <v>3</v>
+      </c>
+      <c r="G29" s="4">
+        <v>50</v>
+      </c>
+      <c r="H29" s="4">
+        <v>400</v>
+      </c>
+      <c r="I29" s="4">
+        <v>10</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="N29" s="2"/>
       <c r="O29" s="4"/>
     </row>
     <row r="30" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C30" s="1"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="C30" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="4">
+        <v>61000011</v>
+      </c>
+      <c r="F30" s="4">
+        <v>3</v>
+      </c>
+      <c r="G30" s="4">
+        <v>150</v>
+      </c>
+      <c r="H30" s="4">
+        <v>450</v>
+      </c>
+      <c r="I30" s="4">
+        <v>10</v>
+      </c>
+      <c r="J30" s="4">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="4"/>
     </row>
     <row r="31" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C31" s="1"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="C31" s="1">
+        <v>1012</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4">
+        <v>61000012</v>
+      </c>
+      <c r="F31" s="4">
+        <v>3</v>
+      </c>
+      <c r="G31" s="4">
+        <v>150</v>
+      </c>
+      <c r="H31" s="4">
+        <v>450</v>
+      </c>
+      <c r="I31" s="4">
+        <v>10</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" s="4"/>
     </row>
     <row r="32" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="C32" s="1">
+        <v>1013</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="4">
+        <v>61000013</v>
+      </c>
+      <c r="F32" s="4">
+        <v>2</v>
+      </c>
+      <c r="G32" s="4">
+        <v>300</v>
+      </c>
+      <c r="H32" s="4">
+        <v>650</v>
+      </c>
+      <c r="I32" s="4">
+        <v>10</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="N32" s="2"/>
       <c r="O32" s="4"/>
     </row>
     <row r="33" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="1"/>
+      <c r="C33" s="1">
+        <v>1014</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="4">
+        <v>61000014</v>
+      </c>
+      <c r="F33" s="4">
+        <v>2</v>
+      </c>
+      <c r="G33" s="4">
+        <v>300</v>
+      </c>
+      <c r="H33" s="4">
+        <v>650</v>
+      </c>
+      <c r="I33" s="4">
+        <v>10</v>
+      </c>
+      <c r="J33" s="4">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="4"/>
     </row>
     <row r="34" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="1"/>
+      <c r="C34" s="1">
+        <v>1015</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="4">
+        <v>61000015</v>
+      </c>
+      <c r="F34" s="4">
+        <v>2</v>
+      </c>
+      <c r="G34" s="4">
+        <v>400</v>
+      </c>
+      <c r="H34" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I34" s="4">
+        <v>10</v>
+      </c>
+      <c r="J34" s="4">
+        <v>0</v>
+      </c>
+      <c r="K34" s="4">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" s="4"/>
     </row>
     <row r="35" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="1"/>
+      <c r="C35" s="1">
+        <v>1016</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="4">
+        <v>61000016</v>
+      </c>
+      <c r="F35" s="4">
+        <v>2</v>
+      </c>
+      <c r="G35" s="4">
+        <v>400</v>
+      </c>
+      <c r="H35" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I35" s="4">
+        <v>10</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="N35" s="2"/>
       <c r="O35" s="4"/>
     </row>
@@ -2527,7 +2734,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:E5 L3:L5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -1660,7 +1660,7 @@
         <v>4028</v>
       </c>
       <c r="F17" s="4">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G17" s="4">
         <v>50</v>
@@ -1980,7 +1980,7 @@
         <v>4029</v>
       </c>
       <c r="F27" s="4">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G27" s="4">
         <v>50</v>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t>#</t>
   </si>
@@ -187,6 +187,33 @@
   </si>
   <si>
     <t>白虎战靴</t>
+  </si>
+  <si>
+    <t>朱雀精华</t>
+  </si>
+  <si>
+    <t>朱雀神剑</t>
+  </si>
+  <si>
+    <t>朱雀神甲</t>
+  </si>
+  <si>
+    <t>朱雀面罩</t>
+  </si>
+  <si>
+    <t>朱雀项链</t>
+  </si>
+  <si>
+    <t>朱雀护腕</t>
+  </si>
+  <si>
+    <t>朱雀护戒</t>
+  </si>
+  <si>
+    <t>朱雀腰带</t>
+  </si>
+  <si>
+    <t>朱雀战靴</t>
   </si>
 </sst>
 </file>
@@ -2290,128 +2317,308 @@
       <c r="O36" s="4"/>
     </row>
     <row r="37" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="1"/>
+      <c r="C37" s="1">
+        <v>1017</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="4">
+        <v>4030</v>
+      </c>
+      <c r="F37" s="4">
+        <v>100</v>
+      </c>
+      <c r="G37" s="4">
+        <v>50</v>
+      </c>
+      <c r="H37" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I37" s="4">
+        <v>10</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" s="4"/>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="1"/>
+      <c r="C38" s="1">
+        <v>1018</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="E38" s="4">
+        <v>61000017</v>
+      </c>
+      <c r="F38" s="4">
+        <v>3</v>
+      </c>
+      <c r="G38" s="4">
+        <v>50</v>
+      </c>
+      <c r="H38" s="4">
+        <v>400</v>
+      </c>
+      <c r="I38" s="4">
+        <v>10</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0</v>
+      </c>
+      <c r="K38" s="4">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="4"/>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="1"/>
+      <c r="C39" s="1">
+        <v>1019</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="4">
+        <v>61000018</v>
+      </c>
+      <c r="F39" s="4">
+        <v>3</v>
+      </c>
+      <c r="G39" s="4">
+        <v>50</v>
+      </c>
+      <c r="H39" s="4">
+        <v>400</v>
+      </c>
+      <c r="I39" s="4">
+        <v>10</v>
+      </c>
+      <c r="J39" s="4">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" s="4"/>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="1"/>
+      <c r="C40" s="1">
+        <v>1020</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="4">
+        <v>61000019</v>
+      </c>
+      <c r="F40" s="4">
+        <v>3</v>
+      </c>
+      <c r="G40" s="4">
+        <v>150</v>
+      </c>
+      <c r="H40" s="4">
+        <v>450</v>
+      </c>
+      <c r="I40" s="4">
+        <v>10</v>
+      </c>
+      <c r="J40" s="4">
+        <v>0</v>
+      </c>
+      <c r="K40" s="4">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="N40" s="2"/>
       <c r="O40" s="4"/>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="1"/>
+      <c r="C41" s="1">
+        <v>1021</v>
+      </c>
+      <c r="D41" s="1">
+        <v>3</v>
+      </c>
+      <c r="E41" s="4">
+        <v>61000020</v>
+      </c>
+      <c r="F41" s="4">
+        <v>3</v>
+      </c>
+      <c r="G41" s="4">
+        <v>150</v>
+      </c>
+      <c r="H41" s="4">
+        <v>450</v>
+      </c>
+      <c r="I41" s="4">
+        <v>10</v>
+      </c>
+      <c r="J41" s="4">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="N41" s="2"/>
       <c r="O41" s="4"/>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C42" s="1"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="1"/>
+      <c r="C42" s="1">
+        <v>1022</v>
+      </c>
+      <c r="D42" s="1">
+        <v>3</v>
+      </c>
+      <c r="E42" s="4">
+        <v>61000021</v>
+      </c>
+      <c r="F42" s="4">
+        <v>2</v>
+      </c>
+      <c r="G42" s="4">
+        <v>300</v>
+      </c>
+      <c r="H42" s="4">
+        <v>650</v>
+      </c>
+      <c r="I42" s="4">
+        <v>10</v>
+      </c>
+      <c r="J42" s="4">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="4"/>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C43" s="1"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="1"/>
+      <c r="C43" s="1">
+        <v>1023</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3</v>
+      </c>
+      <c r="E43" s="4">
+        <v>61000022</v>
+      </c>
+      <c r="F43" s="4">
+        <v>2</v>
+      </c>
+      <c r="G43" s="4">
+        <v>300</v>
+      </c>
+      <c r="H43" s="4">
+        <v>650</v>
+      </c>
+      <c r="I43" s="4">
+        <v>10</v>
+      </c>
+      <c r="J43" s="4">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="4"/>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C44" s="1"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="5"/>
+      <c r="C44" s="1">
+        <v>1024</v>
+      </c>
+      <c r="D44" s="1">
+        <v>3</v>
+      </c>
+      <c r="E44" s="4">
+        <v>61000023</v>
+      </c>
+      <c r="F44" s="4">
+        <v>2</v>
+      </c>
+      <c r="G44" s="4">
+        <v>400</v>
+      </c>
+      <c r="H44" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I44" s="4">
+        <v>10</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="4"/>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C45" s="1"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="1"/>
+      <c r="C45" s="1">
+        <v>1025</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3</v>
+      </c>
+      <c r="E45" s="4">
+        <v>61000024</v>
+      </c>
+      <c r="F45" s="4">
+        <v>2</v>
+      </c>
+      <c r="G45" s="4">
+        <v>400</v>
+      </c>
+      <c r="H45" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I45" s="4">
+        <v>10</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" s="4"/>
     </row>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
   <si>
     <t>#</t>
   </si>
@@ -214,6 +214,33 @@
   </si>
   <si>
     <t>朱雀战靴</t>
+  </si>
+  <si>
+    <t>玄武精华</t>
+  </si>
+  <si>
+    <t>玄武神剑</t>
+  </si>
+  <si>
+    <t>玄武神甲</t>
+  </si>
+  <si>
+    <t>玄武面罩</t>
+  </si>
+  <si>
+    <t>玄武项链</t>
+  </si>
+  <si>
+    <t>玄武护腕</t>
+  </si>
+  <si>
+    <t>玄武护戒</t>
+  </si>
+  <si>
+    <t>玄武腰带</t>
+  </si>
+  <si>
+    <t>玄武战靴</t>
   </si>
 </sst>
 </file>
@@ -1201,8 +1228,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="11" width="14.4159292035398" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.2477876106195" style="1" customWidth="1"/>
+    <col min="5" max="11" width="14.4166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.25" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2628,128 +2655,308 @@
       <c r="O46" s="4"/>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="1"/>
+      <c r="C47" s="1">
+        <v>1026</v>
+      </c>
+      <c r="D47" s="1">
+        <v>4</v>
+      </c>
+      <c r="E47" s="4">
+        <v>4031</v>
+      </c>
+      <c r="F47" s="4">
+        <v>110</v>
+      </c>
+      <c r="G47" s="4">
+        <v>50</v>
+      </c>
+      <c r="H47" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I47" s="4">
+        <v>10</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" s="4"/>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="1"/>
+      <c r="C48" s="1">
+        <v>1027</v>
+      </c>
+      <c r="D48" s="1">
+        <v>4</v>
+      </c>
+      <c r="E48" s="4">
+        <v>61000025</v>
+      </c>
+      <c r="F48" s="4">
+        <v>3</v>
+      </c>
+      <c r="G48" s="4">
+        <v>50</v>
+      </c>
+      <c r="H48" s="4">
+        <v>400</v>
+      </c>
+      <c r="I48" s="4">
+        <v>10</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" s="4"/>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="1"/>
+      <c r="C49" s="1">
+        <v>1028</v>
+      </c>
+      <c r="D49" s="1">
+        <v>4</v>
+      </c>
+      <c r="E49" s="4">
+        <v>61000026</v>
+      </c>
+      <c r="F49" s="4">
+        <v>3</v>
+      </c>
+      <c r="G49" s="4">
+        <v>50</v>
+      </c>
+      <c r="H49" s="4">
+        <v>400</v>
+      </c>
+      <c r="I49" s="4">
+        <v>10</v>
+      </c>
+      <c r="J49" s="4">
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <v>0</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="N49" s="2"/>
       <c r="O49" s="4"/>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="1"/>
+      <c r="C50" s="1">
+        <v>1029</v>
+      </c>
+      <c r="D50" s="1">
+        <v>4</v>
+      </c>
+      <c r="E50" s="4">
+        <v>61000027</v>
+      </c>
+      <c r="F50" s="4">
+        <v>3</v>
+      </c>
+      <c r="G50" s="4">
+        <v>150</v>
+      </c>
+      <c r="H50" s="4">
+        <v>450</v>
+      </c>
+      <c r="I50" s="4">
+        <v>10</v>
+      </c>
+      <c r="J50" s="4">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="N50" s="2"/>
       <c r="O50" s="4"/>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="1"/>
+      <c r="C51" s="1">
+        <v>1030</v>
+      </c>
+      <c r="D51" s="1">
+        <v>4</v>
+      </c>
+      <c r="E51" s="4">
+        <v>61000028</v>
+      </c>
+      <c r="F51" s="4">
+        <v>3</v>
+      </c>
+      <c r="G51" s="4">
+        <v>150</v>
+      </c>
+      <c r="H51" s="4">
+        <v>450</v>
+      </c>
+      <c r="I51" s="4">
+        <v>10</v>
+      </c>
+      <c r="J51" s="4">
+        <v>0</v>
+      </c>
+      <c r="K51" s="4">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="N51" s="2"/>
       <c r="O51" s="4"/>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="1"/>
+      <c r="C52" s="1">
+        <v>1031</v>
+      </c>
+      <c r="D52" s="1">
+        <v>4</v>
+      </c>
+      <c r="E52" s="4">
+        <v>61000029</v>
+      </c>
+      <c r="F52" s="4">
+        <v>2</v>
+      </c>
+      <c r="G52" s="4">
+        <v>300</v>
+      </c>
+      <c r="H52" s="4">
+        <v>650</v>
+      </c>
+      <c r="I52" s="4">
+        <v>10</v>
+      </c>
+      <c r="J52" s="4">
+        <v>0</v>
+      </c>
+      <c r="K52" s="4">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="4"/>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="1"/>
+      <c r="C53" s="1">
+        <v>1032</v>
+      </c>
+      <c r="D53" s="1">
+        <v>4</v>
+      </c>
+      <c r="E53" s="4">
+        <v>61000030</v>
+      </c>
+      <c r="F53" s="4">
+        <v>2</v>
+      </c>
+      <c r="G53" s="4">
+        <v>300</v>
+      </c>
+      <c r="H53" s="4">
+        <v>650</v>
+      </c>
+      <c r="I53" s="4">
+        <v>10</v>
+      </c>
+      <c r="J53" s="4">
+        <v>0</v>
+      </c>
+      <c r="K53" s="4">
+        <v>0</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="N53" s="2"/>
       <c r="O53" s="4"/>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="1"/>
+      <c r="C54" s="1">
+        <v>1033</v>
+      </c>
+      <c r="D54" s="1">
+        <v>4</v>
+      </c>
+      <c r="E54" s="4">
+        <v>61000031</v>
+      </c>
+      <c r="F54" s="4">
+        <v>2</v>
+      </c>
+      <c r="G54" s="4">
+        <v>400</v>
+      </c>
+      <c r="H54" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I54" s="4">
+        <v>10</v>
+      </c>
+      <c r="J54" s="4">
+        <v>0</v>
+      </c>
+      <c r="K54" s="4">
+        <v>0</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="4"/>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="1"/>
+      <c r="C55" s="1">
+        <v>1034</v>
+      </c>
+      <c r="D55" s="1">
+        <v>4</v>
+      </c>
+      <c r="E55" s="4">
+        <v>61000032</v>
+      </c>
+      <c r="F55" s="4">
+        <v>2</v>
+      </c>
+      <c r="G55" s="4">
+        <v>400</v>
+      </c>
+      <c r="H55" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I55" s="4">
+        <v>10</v>
+      </c>
+      <c r="J55" s="4">
+        <v>0</v>
+      </c>
+      <c r="K55" s="4">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="4"/>
     </row>
@@ -2783,30 +2990,90 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="1"/>
       <c r="O58" s="4"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="5:15">
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="1"/>
       <c r="N59" s="2"/>
       <c r="O59" s="4"/>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="1"/>
       <c r="O60" s="4"/>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="1"/>
       <c r="O61" s="4"/>
     </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="5:15">
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="1"/>
       <c r="N62" s="2"/>
       <c r="O62" s="4"/>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="5:15">
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="1"/>
       <c r="N63" s="2"/>
       <c r="O63" s="4"/>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="5"/>
       <c r="M64" s="1"/>
       <c r="N64" s="2"/>
       <c r="O64" s="4"/>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="68">
   <si>
     <t>#</t>
   </si>
@@ -241,6 +241,33 @@
   </si>
   <si>
     <t>玄武战靴</t>
+  </si>
+  <si>
+    <t>麒麟精华</t>
+  </si>
+  <si>
+    <t>麒麟神剑</t>
+  </si>
+  <si>
+    <t>麒麟神甲</t>
+  </si>
+  <si>
+    <t>麒麟面罩</t>
+  </si>
+  <si>
+    <t>麒麟项链</t>
+  </si>
+  <si>
+    <t>麒麟护腕</t>
+  </si>
+  <si>
+    <t>麒麟护戒</t>
+  </si>
+  <si>
+    <t>麒麟腰带</t>
+  </si>
+  <si>
+    <t>麒麟战靴</t>
   </si>
 </sst>
 </file>
@@ -431,12 +458,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1233,17 +1260,17 @@
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="12:12">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="12:12">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="L2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1275,7 +1302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1307,7 +1334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1714,7 +1741,7 @@
         <v>4028</v>
       </c>
       <c r="F17" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G17" s="4">
         <v>50</v>
@@ -2034,7 +2061,7 @@
         <v>4029</v>
       </c>
       <c r="F27" s="4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G27" s="4">
         <v>50</v>
@@ -2354,7 +2381,7 @@
         <v>4030</v>
       </c>
       <c r="F37" s="4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G37" s="4">
         <v>50</v>
@@ -2665,7 +2692,7 @@
         <v>4031</v>
       </c>
       <c r="F47" s="4">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G47" s="4">
         <v>50</v>
@@ -2975,170 +3002,366 @@
       <c r="O56" s="4"/>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="1"/>
+      <c r="C57" s="1">
+        <v>1035</v>
+      </c>
+      <c r="D57" s="1">
+        <v>5</v>
+      </c>
+      <c r="E57" s="4">
+        <v>4032</v>
+      </c>
+      <c r="F57" s="4">
+        <v>150</v>
+      </c>
+      <c r="G57" s="4">
+        <v>50</v>
+      </c>
+      <c r="H57" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I57" s="4">
+        <v>10</v>
+      </c>
+      <c r="J57" s="4">
+        <v>0</v>
+      </c>
+      <c r="K57" s="4">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="4"/>
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="1"/>
+      <c r="C58" s="1">
+        <v>1036</v>
+      </c>
+      <c r="D58" s="1">
+        <v>5</v>
+      </c>
+      <c r="E58" s="4">
+        <v>61000033</v>
+      </c>
+      <c r="F58" s="4">
+        <v>2</v>
+      </c>
+      <c r="G58" s="4">
+        <v>50</v>
+      </c>
+      <c r="H58" s="4">
+        <v>400</v>
+      </c>
+      <c r="I58" s="4">
+        <v>10</v>
+      </c>
+      <c r="J58" s="4">
+        <v>0</v>
+      </c>
+      <c r="K58" s="4">
+        <v>0</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="O58" s="4"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="5:15">
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="1"/>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C59" s="1">
+        <v>1037</v>
+      </c>
+      <c r="D59" s="1">
+        <v>5</v>
+      </c>
+      <c r="E59" s="4">
+        <v>61000034</v>
+      </c>
+      <c r="F59" s="4">
+        <v>2</v>
+      </c>
+      <c r="G59" s="4">
+        <v>50</v>
+      </c>
+      <c r="H59" s="4">
+        <v>400</v>
+      </c>
+      <c r="I59" s="4">
+        <v>10</v>
+      </c>
+      <c r="J59" s="4">
+        <v>0</v>
+      </c>
+      <c r="K59" s="4">
+        <v>0</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="N59" s="2"/>
       <c r="O59" s="4"/>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="1"/>
+      <c r="C60" s="1">
+        <v>1038</v>
+      </c>
+      <c r="D60" s="1">
+        <v>5</v>
+      </c>
+      <c r="E60" s="4">
+        <v>61000035</v>
+      </c>
+      <c r="F60" s="4">
+        <v>2</v>
+      </c>
+      <c r="G60" s="4">
+        <v>150</v>
+      </c>
+      <c r="H60" s="4">
+        <v>450</v>
+      </c>
+      <c r="I60" s="4">
+        <v>10</v>
+      </c>
+      <c r="J60" s="4">
+        <v>0</v>
+      </c>
+      <c r="K60" s="4">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="O60" s="4"/>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="1"/>
+      <c r="C61" s="1">
+        <v>1039</v>
+      </c>
+      <c r="D61" s="1">
+        <v>5</v>
+      </c>
+      <c r="E61" s="4">
+        <v>61000036</v>
+      </c>
+      <c r="F61" s="4">
+        <v>2</v>
+      </c>
+      <c r="G61" s="4">
+        <v>150</v>
+      </c>
+      <c r="H61" s="4">
+        <v>450</v>
+      </c>
+      <c r="I61" s="4">
+        <v>10</v>
+      </c>
+      <c r="J61" s="4">
+        <v>0</v>
+      </c>
+      <c r="K61" s="4">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="O61" s="4"/>
     </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="5:15">
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="1"/>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C62" s="1">
+        <v>1040</v>
+      </c>
+      <c r="D62" s="1">
+        <v>5</v>
+      </c>
+      <c r="E62" s="4">
+        <v>61000037</v>
+      </c>
+      <c r="F62" s="4">
+        <v>2</v>
+      </c>
+      <c r="G62" s="4">
+        <v>300</v>
+      </c>
+      <c r="H62" s="4">
+        <v>650</v>
+      </c>
+      <c r="I62" s="4">
+        <v>10</v>
+      </c>
+      <c r="J62" s="4">
+        <v>0</v>
+      </c>
+      <c r="K62" s="4">
+        <v>0</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="N62" s="2"/>
       <c r="O62" s="4"/>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="5:15">
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="1"/>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C63" s="1">
+        <v>1041</v>
+      </c>
+      <c r="D63" s="1">
+        <v>5</v>
+      </c>
+      <c r="E63" s="4">
+        <v>61000038</v>
+      </c>
+      <c r="F63" s="4">
+        <v>2</v>
+      </c>
+      <c r="G63" s="4">
+        <v>300</v>
+      </c>
+      <c r="H63" s="4">
+        <v>650</v>
+      </c>
+      <c r="I63" s="4">
+        <v>10</v>
+      </c>
+      <c r="J63" s="4">
+        <v>0</v>
+      </c>
+      <c r="K63" s="4">
+        <v>0</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="N63" s="2"/>
       <c r="O63" s="4"/>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="5"/>
+      <c r="C64" s="1">
+        <v>1042</v>
+      </c>
+      <c r="D64" s="1">
+        <v>5</v>
+      </c>
+      <c r="E64" s="4">
+        <v>61000039</v>
+      </c>
+      <c r="F64" s="4">
+        <v>2</v>
+      </c>
+      <c r="G64" s="4">
+        <v>400</v>
+      </c>
+      <c r="H64" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I64" s="4">
+        <v>10</v>
+      </c>
+      <c r="J64" s="4">
+        <v>0</v>
+      </c>
+      <c r="K64" s="4">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="M64" s="1"/>
       <c r="N64" s="2"/>
       <c r="O64" s="4"/>
     </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C65" s="1">
+        <v>1043</v>
+      </c>
+      <c r="D65" s="1">
+        <v>5</v>
+      </c>
+      <c r="E65" s="4">
+        <v>61000040</v>
+      </c>
+      <c r="F65" s="4">
+        <v>2</v>
+      </c>
+      <c r="G65" s="4">
+        <v>400</v>
+      </c>
+      <c r="H65" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I65" s="4">
+        <v>10</v>
+      </c>
+      <c r="J65" s="4">
+        <v>0</v>
+      </c>
+      <c r="K65" s="4">
+        <v>0</v>
+      </c>
+      <c r="L65" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="N65" s="2"/>
       <c r="O65" s="4"/>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N66" s="2"/>
       <c r="O66" s="4"/>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N67" s="2"/>
       <c r="O67" s="4"/>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N68" s="2"/>
       <c r="O68" s="4"/>
     </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N69" s="2"/>
       <c r="O69" s="4"/>
     </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N70" s="2"/>
       <c r="O70" s="4"/>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N71" s="2"/>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N72" s="2"/>
       <c r="O72" s="4"/>
     </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N73" s="2"/>
       <c r="O73" s="4"/>
     </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N74" s="2"/>
       <c r="O74" s="4"/>
     </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N75" s="2"/>
       <c r="O75" s="4"/>
     </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N76" s="2"/>
       <c r="O76" s="4"/>
     </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N77" s="2"/>
       <c r="O77" s="4"/>
     </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N78" s="2"/>
       <c r="O78" s="4"/>
     </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N79" s="2"/>
       <c r="O79" s="4"/>
     </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N80" s="2"/>
       <c r="O80" s="4"/>
     </row>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -1741,7 +1741,7 @@
         <v>4028</v>
       </c>
       <c r="F17" s="4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G17" s="4">
         <v>50</v>
@@ -2061,7 +2061,7 @@
         <v>4029</v>
       </c>
       <c r="F27" s="4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G27" s="4">
         <v>50</v>
@@ -2381,7 +2381,7 @@
         <v>4030</v>
       </c>
       <c r="F37" s="4">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G37" s="4">
         <v>50</v>
@@ -2692,7 +2692,7 @@
         <v>4031</v>
       </c>
       <c r="F47" s="4">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G47" s="4">
         <v>50</v>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
   <si>
     <t>#</t>
   </si>
@@ -96,6 +96,9 @@
     <t>ExcludeLevel</t>
   </si>
   <si>
+    <t>Max</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -135,6 +138,45 @@
     <t>韧性宝石</t>
   </si>
   <si>
+    <t>极·攻击宝石</t>
+  </si>
+  <si>
+    <t>极·韧性宝石</t>
+  </si>
+  <si>
+    <t>极·生命宝石</t>
+  </si>
+  <si>
+    <t>极·命中宝石</t>
+  </si>
+  <si>
+    <t>极·闪避宝石</t>
+  </si>
+  <si>
+    <t>极·物攻宝石</t>
+  </si>
+  <si>
+    <t>极·魔攻宝石</t>
+  </si>
+  <si>
+    <t>极·道攻宝石</t>
+  </si>
+  <si>
+    <t>极·增伤宝石</t>
+  </si>
+  <si>
+    <t>极·破韧宝石</t>
+  </si>
+  <si>
+    <t>极·物伤宝石</t>
+  </si>
+  <si>
+    <t>极·魔伤宝石</t>
+  </si>
+  <si>
+    <t>极·道伤宝石</t>
+  </si>
+  <si>
     <t>青龙精华</t>
   </si>
   <si>
@@ -268,6 +310,33 @@
   </si>
   <si>
     <t>麒麟战靴</t>
+  </si>
+  <si>
+    <t>青龙精粹</t>
+  </si>
+  <si>
+    <t>极青神剑</t>
+  </si>
+  <si>
+    <t>极青神甲</t>
+  </si>
+  <si>
+    <t>极青面罩</t>
+  </si>
+  <si>
+    <t>极青项链</t>
+  </si>
+  <si>
+    <t>极青护腕</t>
+  </si>
+  <si>
+    <t>极青护戒</t>
+  </si>
+  <si>
+    <t>极青腰带</t>
+  </si>
+  <si>
+    <t>极青战靴</t>
   </si>
 </sst>
 </file>
@@ -458,12 +527,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1251,26 +1320,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O96"/>
+  <dimension ref="C1:P110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="11" width="14.4166666666667" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.25" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="5" max="12" width="14.4166666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="L2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1301,8 +1370,11 @@
       <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1333,40 +1405,46 @@
       <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="M5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1394,14 +1472,17 @@
       <c r="K6" s="4">
         <v>10</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M6" s="2"/>
+      <c r="L6" s="4">
+        <v>999</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="N6" s="2"/>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O6" s="2"/>
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1429,14 +1510,17 @@
       <c r="K7" s="4">
         <v>10</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M7" s="2"/>
+      <c r="L7" s="4">
+        <v>999</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="N7" s="2"/>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O7" s="2"/>
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1464,14 +1548,17 @@
       <c r="K8" s="4">
         <v>10</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:15">
+      <c r="L8" s="4">
+        <v>999</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:16">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1499,14 +1586,17 @@
       <c r="K9" s="4">
         <v>10</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="L9" s="4">
+        <v>999</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="1"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1534,14 +1624,17 @@
       <c r="K10" s="4">
         <v>10</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="L10" s="4">
+        <v>999</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="1"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1569,14 +1662,17 @@
       <c r="K11" s="4">
         <v>10</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="4"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="L11" s="4">
+        <v>999</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="1"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="4"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1604,14 +1700,17 @@
       <c r="K12" s="4">
         <v>10</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="4"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="L12" s="4">
+        <v>999</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" s="1"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="4"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1639,14 +1738,17 @@
       <c r="K13" s="4">
         <v>10</v>
       </c>
-      <c r="L13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="4"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="L13" s="4">
+        <v>999</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="4"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1674,14 +1776,17 @@
       <c r="K14" s="4">
         <v>10</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="4"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="L14" s="4">
+        <v>999</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="1"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="4"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1709,14 +1814,17 @@
       <c r="K15" s="4">
         <v>10</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="4"/>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="3:15">
+      <c r="L15" s="4">
+        <v>999</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="4"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="3:16">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="4"/>
@@ -1726,1712 +1834,2644 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="4"/>
-    </row>
-    <row r="17" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C17" s="1">
+      <c r="L16" s="4"/>
+      <c r="M16" s="1"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="4"/>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C17" s="2">
+        <v>11</v>
+      </c>
+      <c r="D17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>60000011</v>
+      </c>
+      <c r="F17" s="1">
+        <v>10</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4">
+        <v>50</v>
+      </c>
+      <c r="K17" s="4">
+        <v>10</v>
+      </c>
+      <c r="L17" s="4">
         <v>999</v>
       </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="M17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="P17" s="4"/>
+    </row>
+    <row r="18" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C18" s="2">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>60000012</v>
+      </c>
+      <c r="F18" s="1">
+        <v>10</v>
+      </c>
+      <c r="G18" s="4">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4">
+        <v>50</v>
+      </c>
+      <c r="K18" s="4">
+        <v>10</v>
+      </c>
+      <c r="L18" s="4">
+        <v>999</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="P18" s="4"/>
+    </row>
+    <row r="19" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C19" s="2">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>60000013</v>
+      </c>
+      <c r="F19" s="1">
+        <v>10</v>
+      </c>
+      <c r="G19" s="4">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4">
+        <v>50</v>
+      </c>
+      <c r="K19" s="4">
+        <v>10</v>
+      </c>
+      <c r="L19" s="4">
+        <v>999</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" s="2"/>
+      <c r="P19" s="4"/>
+    </row>
+    <row r="20" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C20" s="2">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E20" s="4">
+        <v>60000014</v>
+      </c>
+      <c r="F20" s="1">
+        <v>10</v>
+      </c>
+      <c r="G20" s="4">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4">
+        <v>50</v>
+      </c>
+      <c r="K20" s="4">
+        <v>10</v>
+      </c>
+      <c r="L20" s="4">
+        <v>999</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20" s="4"/>
+    </row>
+    <row r="21" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C21" s="2">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E21" s="4">
+        <v>60000015</v>
+      </c>
+      <c r="F21" s="1">
+        <v>10</v>
+      </c>
+      <c r="G21" s="4">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1</v>
+      </c>
+      <c r="J21" s="4">
+        <v>50</v>
+      </c>
+      <c r="K21" s="4">
+        <v>10</v>
+      </c>
+      <c r="L21" s="4">
+        <v>999</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="4"/>
+    </row>
+    <row r="22" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C22" s="2">
+        <v>16</v>
+      </c>
+      <c r="D22" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>60000016</v>
+      </c>
+      <c r="F22" s="1">
+        <v>10</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1</v>
+      </c>
+      <c r="J22" s="4">
+        <v>50</v>
+      </c>
+      <c r="K22" s="4">
+        <v>10</v>
+      </c>
+      <c r="L22" s="4">
+        <v>999</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" s="2"/>
+      <c r="P22" s="4"/>
+    </row>
+    <row r="23" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C23" s="2">
+        <v>17</v>
+      </c>
+      <c r="D23" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E23" s="4">
+        <v>60000017</v>
+      </c>
+      <c r="F23" s="1">
+        <v>10</v>
+      </c>
+      <c r="G23" s="4">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1</v>
+      </c>
+      <c r="J23" s="4">
+        <v>50</v>
+      </c>
+      <c r="K23" s="4">
+        <v>10</v>
+      </c>
+      <c r="L23" s="4">
+        <v>999</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O23" s="2"/>
+      <c r="P23" s="4"/>
+    </row>
+    <row r="24" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C24" s="2">
+        <v>18</v>
+      </c>
+      <c r="D24" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>60000018</v>
+      </c>
+      <c r="F24" s="1">
+        <v>10</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4">
+        <v>50</v>
+      </c>
+      <c r="K24" s="4">
+        <v>10</v>
+      </c>
+      <c r="L24" s="4">
+        <v>999</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="4"/>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C25" s="2">
+        <v>19</v>
+      </c>
+      <c r="D25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E25" s="4">
+        <v>60000019</v>
+      </c>
+      <c r="F25" s="1">
+        <v>10</v>
+      </c>
+      <c r="G25" s="4">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4">
+        <v>50</v>
+      </c>
+      <c r="K25" s="4">
+        <v>10</v>
+      </c>
+      <c r="L25" s="4">
+        <v>999</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" s="4"/>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C26" s="2">
+        <v>20</v>
+      </c>
+      <c r="D26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E26" s="4">
+        <v>60000020</v>
+      </c>
+      <c r="F26" s="1">
+        <v>10</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4">
+        <v>50</v>
+      </c>
+      <c r="K26" s="4">
+        <v>10</v>
+      </c>
+      <c r="L26" s="4">
+        <v>999</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" s="4"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C27" s="2">
+        <v>21</v>
+      </c>
+      <c r="D27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E27" s="4">
+        <v>60000021</v>
+      </c>
+      <c r="F27" s="1">
+        <v>10</v>
+      </c>
+      <c r="G27" s="4">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4">
+        <v>50</v>
+      </c>
+      <c r="K27" s="4">
+        <v>10</v>
+      </c>
+      <c r="L27" s="4">
+        <v>999</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O27" s="2"/>
+      <c r="P27" s="4"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C28" s="2">
+        <v>22</v>
+      </c>
+      <c r="D28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E28" s="4">
+        <v>60000022</v>
+      </c>
+      <c r="F28" s="1">
+        <v>10</v>
+      </c>
+      <c r="G28" s="4">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1</v>
+      </c>
+      <c r="J28" s="4">
+        <v>50</v>
+      </c>
+      <c r="K28" s="4">
+        <v>10</v>
+      </c>
+      <c r="L28" s="4">
+        <v>999</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" s="4"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C29" s="2">
+        <v>23</v>
+      </c>
+      <c r="D29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="E29" s="4">
+        <v>60000023</v>
+      </c>
+      <c r="F29" s="1">
+        <v>10</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4">
+        <v>50</v>
+      </c>
+      <c r="K29" s="4">
+        <v>10</v>
+      </c>
+      <c r="L29" s="4">
+        <v>999</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" s="4"/>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="1"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="4"/>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C31" s="1">
+        <v>999</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4">
         <v>4028</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F31" s="4">
         <v>85</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G31" s="4">
         <v>50</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H31" s="4">
         <v>1000</v>
       </c>
-      <c r="I17" s="4">
-        <v>10</v>
-      </c>
-      <c r="J17" s="4">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="4"/>
-    </row>
-    <row r="18" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C18" s="2">
+      <c r="I31" s="4">
+        <v>10</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4">
+        <v>999</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" s="2"/>
+      <c r="P31" s="4"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C32" s="2">
         <v>1000</v>
       </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4">
         <v>61000001</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F32" s="4">
         <v>3</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G32" s="4">
         <v>50</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H32" s="4">
         <v>400</v>
       </c>
-      <c r="I18" s="4">
-        <v>10</v>
-      </c>
-      <c r="J18" s="4">
-        <v>0</v>
-      </c>
-      <c r="K18" s="4">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="4"/>
-    </row>
-    <row r="19" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C19" s="2">
+      <c r="I32" s="4">
+        <v>10</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4">
+        <v>5</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" s="4"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C33" s="2">
         <v>1001</v>
       </c>
-      <c r="D19" s="2">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4">
         <v>61000002</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F33" s="4">
         <v>3</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G33" s="4">
         <v>50</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H33" s="4">
         <v>400</v>
       </c>
-      <c r="I19" s="4">
-        <v>10</v>
-      </c>
-      <c r="J19" s="4">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4">
-        <v>0</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="4"/>
-    </row>
-    <row r="20" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C20" s="2">
+      <c r="I33" s="4">
+        <v>10</v>
+      </c>
+      <c r="J33" s="4">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4">
+        <v>5</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" s="4"/>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C34" s="2">
         <v>1002</v>
       </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="D34" s="2">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4">
         <v>61000003</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F34" s="4">
         <v>3</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G34" s="4">
         <v>150</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H34" s="4">
         <v>450</v>
       </c>
-      <c r="I20" s="4">
-        <v>10</v>
-      </c>
-      <c r="J20" s="4">
-        <v>0</v>
-      </c>
-      <c r="K20" s="4">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="4"/>
-    </row>
-    <row r="21" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C21" s="2">
+      <c r="I34" s="4">
+        <v>10</v>
+      </c>
+      <c r="J34" s="4">
+        <v>0</v>
+      </c>
+      <c r="K34" s="4">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4">
+        <v>5</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" s="4"/>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C35" s="2">
         <v>1003</v>
       </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="4">
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" s="4">
         <v>61000004</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F35" s="4">
         <v>3</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G35" s="4">
         <v>150</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H35" s="4">
         <v>450</v>
       </c>
-      <c r="I21" s="4">
-        <v>10</v>
-      </c>
-      <c r="J21" s="4">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="4"/>
-    </row>
-    <row r="22" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C22" s="2">
+      <c r="I35" s="4">
+        <v>10</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0</v>
+      </c>
+      <c r="L35" s="4">
+        <v>5</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" s="4"/>
+    </row>
+    <row r="36" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C36" s="2">
         <v>1004</v>
       </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4">
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4">
         <v>61000005</v>
       </c>
-      <c r="F22" s="4">
-        <v>2</v>
-      </c>
-      <c r="G22" s="4">
+      <c r="F36" s="4">
+        <v>2</v>
+      </c>
+      <c r="G36" s="4">
         <v>300</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H36" s="4">
         <v>650</v>
       </c>
-      <c r="I22" s="4">
-        <v>10</v>
-      </c>
-      <c r="J22" s="4">
-        <v>0</v>
-      </c>
-      <c r="K22" s="4">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="4"/>
-    </row>
-    <row r="23" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C23" s="2">
+      <c r="I36" s="4">
+        <v>10</v>
+      </c>
+      <c r="J36" s="4">
+        <v>0</v>
+      </c>
+      <c r="K36" s="4">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4">
+        <v>5</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" s="4"/>
+    </row>
+    <row r="37" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C37" s="2">
         <v>1005</v>
       </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" s="4">
+      <c r="D37" s="2">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4">
         <v>61000006</v>
       </c>
-      <c r="F23" s="4">
-        <v>2</v>
-      </c>
-      <c r="G23" s="4">
+      <c r="F37" s="4">
+        <v>2</v>
+      </c>
+      <c r="G37" s="4">
         <v>300</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H37" s="4">
         <v>650</v>
       </c>
-      <c r="I23" s="4">
-        <v>10</v>
-      </c>
-      <c r="J23" s="4">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="4"/>
-    </row>
-    <row r="24" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C24" s="2">
+      <c r="I37" s="4">
+        <v>10</v>
+      </c>
+      <c r="J37" s="4">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4">
+        <v>5</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" s="4"/>
+    </row>
+    <row r="38" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C38" s="2">
         <v>1006</v>
       </c>
-      <c r="D24" s="2">
-        <v>1</v>
-      </c>
-      <c r="E24" s="4">
+      <c r="D38" s="2">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4">
         <v>61000007</v>
       </c>
-      <c r="F24" s="4">
-        <v>2</v>
-      </c>
-      <c r="G24" s="4">
+      <c r="F38" s="4">
+        <v>2</v>
+      </c>
+      <c r="G38" s="4">
         <v>400</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H38" s="4">
         <v>1000</v>
       </c>
-      <c r="I24" s="4">
-        <v>10</v>
-      </c>
-      <c r="J24" s="4">
-        <v>0</v>
-      </c>
-      <c r="K24" s="4">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="4"/>
-    </row>
-    <row r="25" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C25" s="2">
+      <c r="I38" s="4">
+        <v>10</v>
+      </c>
+      <c r="J38" s="4">
+        <v>0</v>
+      </c>
+      <c r="K38" s="4">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4">
+        <v>5</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" s="4"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C39" s="2">
         <v>1007</v>
       </c>
-      <c r="D25" s="2">
-        <v>1</v>
-      </c>
-      <c r="E25" s="4">
+      <c r="D39" s="2">
+        <v>1</v>
+      </c>
+      <c r="E39" s="4">
         <v>61000008</v>
       </c>
-      <c r="F25" s="4">
-        <v>2</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="F39" s="4">
+        <v>2</v>
+      </c>
+      <c r="G39" s="4">
         <v>400</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H39" s="4">
         <v>1000</v>
       </c>
-      <c r="I25" s="4">
-        <v>10</v>
-      </c>
-      <c r="J25" s="4">
-        <v>0</v>
-      </c>
-      <c r="K25" s="4">
-        <v>0</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="4"/>
-    </row>
-    <row r="26" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="4"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C27" s="1">
+      <c r="I39" s="4">
+        <v>10</v>
+      </c>
+      <c r="J39" s="4">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4">
+        <v>5</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" s="4"/>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="1"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="4"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C41" s="1">
         <v>1008</v>
       </c>
-      <c r="D27" s="1">
-        <v>2</v>
-      </c>
-      <c r="E27" s="4">
+      <c r="D41" s="1">
+        <v>2</v>
+      </c>
+      <c r="E41" s="4">
         <v>4029</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F41" s="4">
         <v>90</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G41" s="4">
         <v>50</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H41" s="4">
         <v>1000</v>
       </c>
-      <c r="I27" s="4">
-        <v>10</v>
-      </c>
-      <c r="J27" s="4">
-        <v>0</v>
-      </c>
-      <c r="K27" s="4">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="4"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C28" s="1">
+      <c r="I41" s="4">
+        <v>10</v>
+      </c>
+      <c r="J41" s="4">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4">
+        <v>999</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" s="4"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C42" s="1">
         <v>1009</v>
       </c>
-      <c r="D28" s="1">
-        <v>2</v>
-      </c>
-      <c r="E28" s="4">
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="4">
         <v>61000009</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F42" s="4">
         <v>3</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G42" s="4">
         <v>50</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H42" s="4">
         <v>400</v>
       </c>
-      <c r="I28" s="4">
-        <v>10</v>
-      </c>
-      <c r="J28" s="4">
-        <v>0</v>
-      </c>
-      <c r="K28" s="4">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="4"/>
-    </row>
-    <row r="29" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C29" s="1">
+      <c r="I42" s="4">
+        <v>10</v>
+      </c>
+      <c r="J42" s="4">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4">
+        <v>0</v>
+      </c>
+      <c r="L42" s="4">
+        <v>5</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" s="4"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C43" s="1">
         <v>1010</v>
       </c>
-      <c r="D29" s="1">
-        <v>2</v>
-      </c>
-      <c r="E29" s="4">
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="4">
         <v>61000010</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F43" s="4">
         <v>3</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G43" s="4">
         <v>50</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H43" s="4">
         <v>400</v>
       </c>
-      <c r="I29" s="4">
-        <v>10</v>
-      </c>
-      <c r="J29" s="4">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="4"/>
-    </row>
-    <row r="30" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C30" s="1">
+      <c r="I43" s="4">
+        <v>10</v>
+      </c>
+      <c r="J43" s="4">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4">
+        <v>5</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" s="4"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C44" s="1">
         <v>1011</v>
       </c>
-      <c r="D30" s="1">
-        <v>2</v>
-      </c>
-      <c r="E30" s="4">
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="4">
         <v>61000011</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F44" s="4">
         <v>3</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G44" s="4">
         <v>150</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H44" s="4">
         <v>450</v>
       </c>
-      <c r="I30" s="4">
-        <v>10</v>
-      </c>
-      <c r="J30" s="4">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="4"/>
-    </row>
-    <row r="31" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C31" s="1">
+      <c r="I44" s="4">
+        <v>10</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4">
+        <v>0</v>
+      </c>
+      <c r="L44" s="4">
+        <v>5</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" s="4"/>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C45" s="1">
         <v>1012</v>
       </c>
-      <c r="D31" s="1">
-        <v>2</v>
-      </c>
-      <c r="E31" s="4">
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="4">
         <v>61000012</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F45" s="4">
         <v>3</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G45" s="4">
         <v>150</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H45" s="4">
         <v>450</v>
       </c>
-      <c r="I31" s="4">
-        <v>10</v>
-      </c>
-      <c r="J31" s="4">
-        <v>0</v>
-      </c>
-      <c r="K31" s="4">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="4"/>
-    </row>
-    <row r="32" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C32" s="1">
+      <c r="I45" s="4">
+        <v>10</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4">
+        <v>0</v>
+      </c>
+      <c r="L45" s="4">
+        <v>5</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" s="4"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C46" s="1">
         <v>1013</v>
       </c>
-      <c r="D32" s="1">
-        <v>2</v>
-      </c>
-      <c r="E32" s="4">
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="4">
         <v>61000013</v>
       </c>
-      <c r="F32" s="4">
-        <v>2</v>
-      </c>
-      <c r="G32" s="4">
+      <c r="F46" s="4">
+        <v>2</v>
+      </c>
+      <c r="G46" s="4">
         <v>300</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H46" s="4">
         <v>650</v>
       </c>
-      <c r="I32" s="4">
-        <v>10</v>
-      </c>
-      <c r="J32" s="4">
-        <v>0</v>
-      </c>
-      <c r="K32" s="4">
-        <v>0</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="4"/>
-    </row>
-    <row r="33" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C33" s="1">
+      <c r="I46" s="4">
+        <v>10</v>
+      </c>
+      <c r="J46" s="4">
+        <v>0</v>
+      </c>
+      <c r="K46" s="4">
+        <v>0</v>
+      </c>
+      <c r="L46" s="4">
+        <v>5</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" s="4"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C47" s="1">
         <v>1014</v>
       </c>
-      <c r="D33" s="1">
-        <v>2</v>
-      </c>
-      <c r="E33" s="4">
+      <c r="D47" s="1">
+        <v>2</v>
+      </c>
+      <c r="E47" s="4">
         <v>61000014</v>
       </c>
-      <c r="F33" s="4">
-        <v>2</v>
-      </c>
-      <c r="G33" s="4">
+      <c r="F47" s="4">
+        <v>2</v>
+      </c>
+      <c r="G47" s="4">
         <v>300</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H47" s="4">
         <v>650</v>
       </c>
-      <c r="I33" s="4">
-        <v>10</v>
-      </c>
-      <c r="J33" s="4">
-        <v>0</v>
-      </c>
-      <c r="K33" s="4">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="4"/>
-    </row>
-    <row r="34" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C34" s="1">
+      <c r="I47" s="4">
+        <v>10</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4">
+        <v>5</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" s="4"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C48" s="1">
         <v>1015</v>
       </c>
-      <c r="D34" s="1">
-        <v>2</v>
-      </c>
-      <c r="E34" s="4">
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="4">
         <v>61000015</v>
       </c>
-      <c r="F34" s="4">
-        <v>2</v>
-      </c>
-      <c r="G34" s="4">
+      <c r="F48" s="4">
+        <v>2</v>
+      </c>
+      <c r="G48" s="4">
         <v>400</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H48" s="4">
         <v>1000</v>
       </c>
-      <c r="I34" s="4">
-        <v>10</v>
-      </c>
-      <c r="J34" s="4">
-        <v>0</v>
-      </c>
-      <c r="K34" s="4">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="4"/>
-    </row>
-    <row r="35" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C35" s="1">
+      <c r="I48" s="4">
+        <v>10</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
+        <v>0</v>
+      </c>
+      <c r="L48" s="4">
+        <v>5</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" s="4"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C49" s="1">
         <v>1016</v>
       </c>
-      <c r="D35" s="1">
-        <v>2</v>
-      </c>
-      <c r="E35" s="4">
+      <c r="D49" s="1">
+        <v>2</v>
+      </c>
+      <c r="E49" s="4">
         <v>61000016</v>
       </c>
-      <c r="F35" s="4">
-        <v>2</v>
-      </c>
-      <c r="G35" s="4">
+      <c r="F49" s="4">
+        <v>2</v>
+      </c>
+      <c r="G49" s="4">
         <v>400</v>
       </c>
-      <c r="H35" s="4">
+      <c r="H49" s="4">
         <v>1000</v>
       </c>
-      <c r="I35" s="4">
-        <v>10</v>
-      </c>
-      <c r="J35" s="4">
-        <v>0</v>
-      </c>
-      <c r="K35" s="4">
-        <v>0</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="4"/>
-    </row>
-    <row r="36" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="1"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="4"/>
-    </row>
-    <row r="37" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C37" s="1">
+      <c r="I49" s="4">
+        <v>10</v>
+      </c>
+      <c r="J49" s="4">
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <v>0</v>
+      </c>
+      <c r="L49" s="4">
+        <v>5</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="O49" s="2"/>
+      <c r="P49" s="4"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="1"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="4"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C51" s="1">
         <v>1017</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D51" s="1">
         <v>3</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E51" s="4">
         <v>4030</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F51" s="4">
         <v>105</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G51" s="4">
         <v>50</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H51" s="4">
         <v>1000</v>
       </c>
-      <c r="I37" s="4">
-        <v>10</v>
-      </c>
-      <c r="J37" s="4">
-        <v>0</v>
-      </c>
-      <c r="K37" s="4">
-        <v>0</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="4"/>
-    </row>
-    <row r="38" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C38" s="1">
+      <c r="I51" s="4">
+        <v>10</v>
+      </c>
+      <c r="J51" s="4">
+        <v>0</v>
+      </c>
+      <c r="K51" s="4">
+        <v>0</v>
+      </c>
+      <c r="L51" s="4">
+        <v>999</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" s="4"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C52" s="1">
         <v>1018</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D52" s="1">
         <v>3</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E52" s="4">
         <v>61000017</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F52" s="4">
         <v>3</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G52" s="4">
         <v>50</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H52" s="4">
         <v>400</v>
       </c>
-      <c r="I38" s="4">
-        <v>10</v>
-      </c>
-      <c r="J38" s="4">
-        <v>0</v>
-      </c>
-      <c r="K38" s="4">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="4"/>
-    </row>
-    <row r="39" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C39" s="1">
+      <c r="I52" s="4">
+        <v>10</v>
+      </c>
+      <c r="J52" s="4">
+        <v>0</v>
+      </c>
+      <c r="K52" s="4">
+        <v>0</v>
+      </c>
+      <c r="L52" s="4">
+        <v>5</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" s="4"/>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C53" s="1">
         <v>1019</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D53" s="1">
         <v>3</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E53" s="4">
         <v>61000018</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F53" s="4">
         <v>3</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G53" s="4">
         <v>50</v>
       </c>
-      <c r="H39" s="4">
+      <c r="H53" s="4">
         <v>400</v>
       </c>
-      <c r="I39" s="4">
-        <v>10</v>
-      </c>
-      <c r="J39" s="4">
-        <v>0</v>
-      </c>
-      <c r="K39" s="4">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="4"/>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C40" s="1">
+      <c r="I53" s="4">
+        <v>10</v>
+      </c>
+      <c r="J53" s="4">
+        <v>0</v>
+      </c>
+      <c r="K53" s="4">
+        <v>0</v>
+      </c>
+      <c r="L53" s="4">
+        <v>5</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" s="4"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C54" s="1">
         <v>1020</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D54" s="1">
         <v>3</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E54" s="4">
         <v>61000019</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F54" s="4">
         <v>3</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G54" s="4">
         <v>150</v>
       </c>
-      <c r="H40" s="4">
+      <c r="H54" s="4">
         <v>450</v>
       </c>
-      <c r="I40" s="4">
-        <v>10</v>
-      </c>
-      <c r="J40" s="4">
-        <v>0</v>
-      </c>
-      <c r="K40" s="4">
-        <v>0</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="4"/>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C41" s="1">
+      <c r="I54" s="4">
+        <v>10</v>
+      </c>
+      <c r="J54" s="4">
+        <v>0</v>
+      </c>
+      <c r="K54" s="4">
+        <v>0</v>
+      </c>
+      <c r="L54" s="4">
+        <v>5</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" s="4"/>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C55" s="1">
         <v>1021</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D55" s="1">
         <v>3</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E55" s="4">
         <v>61000020</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F55" s="4">
         <v>3</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G55" s="4">
         <v>150</v>
       </c>
-      <c r="H41" s="4">
+      <c r="H55" s="4">
         <v>450</v>
       </c>
-      <c r="I41" s="4">
-        <v>10</v>
-      </c>
-      <c r="J41" s="4">
-        <v>0</v>
-      </c>
-      <c r="K41" s="4">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="4"/>
-    </row>
-    <row r="42" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C42" s="1">
+      <c r="I55" s="4">
+        <v>10</v>
+      </c>
+      <c r="J55" s="4">
+        <v>0</v>
+      </c>
+      <c r="K55" s="4">
+        <v>0</v>
+      </c>
+      <c r="L55" s="4">
+        <v>5</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" s="4"/>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C56" s="1">
         <v>1022</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D56" s="1">
         <v>3</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E56" s="4">
         <v>61000021</v>
       </c>
-      <c r="F42" s="4">
-        <v>2</v>
-      </c>
-      <c r="G42" s="4">
+      <c r="F56" s="4">
+        <v>2</v>
+      </c>
+      <c r="G56" s="4">
         <v>300</v>
       </c>
-      <c r="H42" s="4">
+      <c r="H56" s="4">
         <v>650</v>
       </c>
-      <c r="I42" s="4">
-        <v>10</v>
-      </c>
-      <c r="J42" s="4">
-        <v>0</v>
-      </c>
-      <c r="K42" s="4">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="4"/>
-    </row>
-    <row r="43" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C43" s="1">
+      <c r="I56" s="4">
+        <v>10</v>
+      </c>
+      <c r="J56" s="4">
+        <v>0</v>
+      </c>
+      <c r="K56" s="4">
+        <v>0</v>
+      </c>
+      <c r="L56" s="4">
+        <v>5</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" s="4"/>
+    </row>
+    <row r="57" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C57" s="1">
         <v>1023</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D57" s="1">
         <v>3</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E57" s="4">
         <v>61000022</v>
       </c>
-      <c r="F43" s="4">
-        <v>2</v>
-      </c>
-      <c r="G43" s="4">
+      <c r="F57" s="4">
+        <v>2</v>
+      </c>
+      <c r="G57" s="4">
         <v>300</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H57" s="4">
         <v>650</v>
       </c>
-      <c r="I43" s="4">
-        <v>10</v>
-      </c>
-      <c r="J43" s="4">
-        <v>0</v>
-      </c>
-      <c r="K43" s="4">
-        <v>0</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="4"/>
-    </row>
-    <row r="44" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C44" s="1">
+      <c r="I57" s="4">
+        <v>10</v>
+      </c>
+      <c r="J57" s="4">
+        <v>0</v>
+      </c>
+      <c r="K57" s="4">
+        <v>0</v>
+      </c>
+      <c r="L57" s="4">
+        <v>5</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" s="4"/>
+    </row>
+    <row r="58" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C58" s="1">
         <v>1024</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D58" s="1">
         <v>3</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E58" s="4">
         <v>61000023</v>
       </c>
-      <c r="F44" s="4">
-        <v>2</v>
-      </c>
-      <c r="G44" s="4">
+      <c r="F58" s="4">
+        <v>2</v>
+      </c>
+      <c r="G58" s="4">
         <v>400</v>
       </c>
-      <c r="H44" s="4">
+      <c r="H58" s="4">
         <v>1000</v>
       </c>
-      <c r="I44" s="4">
-        <v>10</v>
-      </c>
-      <c r="J44" s="4">
-        <v>0</v>
-      </c>
-      <c r="K44" s="4">
-        <v>0</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="4"/>
-    </row>
-    <row r="45" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C45" s="1">
+      <c r="I58" s="4">
+        <v>10</v>
+      </c>
+      <c r="J58" s="4">
+        <v>0</v>
+      </c>
+      <c r="K58" s="4">
+        <v>0</v>
+      </c>
+      <c r="L58" s="4">
+        <v>5</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" s="4"/>
+    </row>
+    <row r="59" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C59" s="1">
         <v>1025</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D59" s="1">
         <v>3</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E59" s="4">
         <v>61000024</v>
       </c>
-      <c r="F45" s="4">
-        <v>2</v>
-      </c>
-      <c r="G45" s="4">
+      <c r="F59" s="4">
+        <v>2</v>
+      </c>
+      <c r="G59" s="4">
         <v>400</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H59" s="4">
         <v>1000</v>
       </c>
-      <c r="I45" s="4">
-        <v>10</v>
-      </c>
-      <c r="J45" s="4">
-        <v>0</v>
-      </c>
-      <c r="K45" s="4">
-        <v>0</v>
-      </c>
-      <c r="L45" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="4"/>
-    </row>
-    <row r="46" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C46" s="1"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="4"/>
-    </row>
-    <row r="47" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C47" s="1">
+      <c r="I59" s="4">
+        <v>10</v>
+      </c>
+      <c r="J59" s="4">
+        <v>0</v>
+      </c>
+      <c r="K59" s="4">
+        <v>0</v>
+      </c>
+      <c r="L59" s="4">
+        <v>5</v>
+      </c>
+      <c r="M59" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" s="4"/>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C60" s="1"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="4"/>
+    </row>
+    <row r="61" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C61" s="1">
         <v>1026</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D61" s="1">
         <v>4</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E61" s="4">
         <v>4031</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F61" s="4">
         <v>115</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G61" s="4">
         <v>50</v>
       </c>
-      <c r="H47" s="4">
+      <c r="H61" s="4">
         <v>1000</v>
       </c>
-      <c r="I47" s="4">
-        <v>10</v>
-      </c>
-      <c r="J47" s="4">
-        <v>0</v>
-      </c>
-      <c r="K47" s="4">
-        <v>0</v>
-      </c>
-      <c r="L47" s="1" t="s">
+      <c r="I61" s="4">
+        <v>10</v>
+      </c>
+      <c r="J61" s="4">
+        <v>0</v>
+      </c>
+      <c r="K61" s="4">
+        <v>0</v>
+      </c>
+      <c r="L61" s="4">
+        <v>999</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" s="4"/>
+    </row>
+    <row r="62" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C62" s="1">
+        <v>1027</v>
+      </c>
+      <c r="D62" s="1">
+        <v>4</v>
+      </c>
+      <c r="E62" s="4">
+        <v>61000025</v>
+      </c>
+      <c r="F62" s="4">
+        <v>3</v>
+      </c>
+      <c r="G62" s="4">
         <v>50</v>
       </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="4"/>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C48" s="1">
-        <v>1027</v>
-      </c>
-      <c r="D48" s="1">
+      <c r="H62" s="4">
+        <v>400</v>
+      </c>
+      <c r="I62" s="4">
+        <v>10</v>
+      </c>
+      <c r="J62" s="4">
+        <v>0</v>
+      </c>
+      <c r="K62" s="4">
+        <v>0</v>
+      </c>
+      <c r="L62" s="4">
+        <v>5</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" s="4"/>
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C63" s="1">
+        <v>1028</v>
+      </c>
+      <c r="D63" s="1">
         <v>4</v>
       </c>
-      <c r="E48" s="4">
-        <v>61000025</v>
-      </c>
-      <c r="F48" s="4">
+      <c r="E63" s="4">
+        <v>61000026</v>
+      </c>
+      <c r="F63" s="4">
         <v>3</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G63" s="4">
         <v>50</v>
       </c>
-      <c r="H48" s="4">
+      <c r="H63" s="4">
         <v>400</v>
       </c>
-      <c r="I48" s="4">
-        <v>10</v>
-      </c>
-      <c r="J48" s="4">
-        <v>0</v>
-      </c>
-      <c r="K48" s="4">
-        <v>0</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="4"/>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C49" s="1">
-        <v>1028</v>
-      </c>
-      <c r="D49" s="1">
+      <c r="I63" s="4">
+        <v>10</v>
+      </c>
+      <c r="J63" s="4">
+        <v>0</v>
+      </c>
+      <c r="K63" s="4">
+        <v>0</v>
+      </c>
+      <c r="L63" s="4">
+        <v>5</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" s="4"/>
+    </row>
+    <row r="64" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C64" s="1">
+        <v>1029</v>
+      </c>
+      <c r="D64" s="1">
         <v>4</v>
       </c>
-      <c r="E49" s="4">
-        <v>61000026</v>
-      </c>
-      <c r="F49" s="4">
+      <c r="E64" s="4">
+        <v>61000027</v>
+      </c>
+      <c r="F64" s="4">
         <v>3</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G64" s="4">
+        <v>150</v>
+      </c>
+      <c r="H64" s="4">
+        <v>450</v>
+      </c>
+      <c r="I64" s="4">
+        <v>10</v>
+      </c>
+      <c r="J64" s="4">
+        <v>0</v>
+      </c>
+      <c r="K64" s="4">
+        <v>0</v>
+      </c>
+      <c r="L64" s="4">
+        <v>5</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" s="4"/>
+    </row>
+    <row r="65" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C65" s="1">
+        <v>1030</v>
+      </c>
+      <c r="D65" s="1">
+        <v>4</v>
+      </c>
+      <c r="E65" s="4">
+        <v>61000028</v>
+      </c>
+      <c r="F65" s="4">
+        <v>3</v>
+      </c>
+      <c r="G65" s="4">
+        <v>150</v>
+      </c>
+      <c r="H65" s="4">
+        <v>450</v>
+      </c>
+      <c r="I65" s="4">
+        <v>10</v>
+      </c>
+      <c r="J65" s="4">
+        <v>0</v>
+      </c>
+      <c r="K65" s="4">
+        <v>0</v>
+      </c>
+      <c r="L65" s="4">
+        <v>5</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" s="4"/>
+    </row>
+    <row r="66" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C66" s="1">
+        <v>1031</v>
+      </c>
+      <c r="D66" s="1">
+        <v>4</v>
+      </c>
+      <c r="E66" s="4">
+        <v>61000029</v>
+      </c>
+      <c r="F66" s="4">
+        <v>2</v>
+      </c>
+      <c r="G66" s="4">
+        <v>300</v>
+      </c>
+      <c r="H66" s="4">
+        <v>650</v>
+      </c>
+      <c r="I66" s="4">
+        <v>10</v>
+      </c>
+      <c r="J66" s="4">
+        <v>0</v>
+      </c>
+      <c r="K66" s="4">
+        <v>0</v>
+      </c>
+      <c r="L66" s="4">
+        <v>5</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" s="4"/>
+    </row>
+    <row r="67" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C67" s="1">
+        <v>1032</v>
+      </c>
+      <c r="D67" s="1">
+        <v>4</v>
+      </c>
+      <c r="E67" s="4">
+        <v>61000030</v>
+      </c>
+      <c r="F67" s="4">
+        <v>2</v>
+      </c>
+      <c r="G67" s="4">
+        <v>300</v>
+      </c>
+      <c r="H67" s="4">
+        <v>650</v>
+      </c>
+      <c r="I67" s="4">
+        <v>10</v>
+      </c>
+      <c r="J67" s="4">
+        <v>0</v>
+      </c>
+      <c r="K67" s="4">
+        <v>0</v>
+      </c>
+      <c r="L67" s="4">
+        <v>5</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" s="4"/>
+    </row>
+    <row r="68" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C68" s="1">
+        <v>1033</v>
+      </c>
+      <c r="D68" s="1">
+        <v>4</v>
+      </c>
+      <c r="E68" s="4">
+        <v>61000031</v>
+      </c>
+      <c r="F68" s="4">
+        <v>2</v>
+      </c>
+      <c r="G68" s="4">
+        <v>400</v>
+      </c>
+      <c r="H68" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I68" s="4">
+        <v>10</v>
+      </c>
+      <c r="J68" s="4">
+        <v>0</v>
+      </c>
+      <c r="K68" s="4">
+        <v>0</v>
+      </c>
+      <c r="L68" s="4">
+        <v>5</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" s="4"/>
+    </row>
+    <row r="69" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C69" s="1">
+        <v>1034</v>
+      </c>
+      <c r="D69" s="1">
+        <v>4</v>
+      </c>
+      <c r="E69" s="4">
+        <v>61000032</v>
+      </c>
+      <c r="F69" s="4">
+        <v>2</v>
+      </c>
+      <c r="G69" s="4">
+        <v>400</v>
+      </c>
+      <c r="H69" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I69" s="4">
+        <v>10</v>
+      </c>
+      <c r="J69" s="4">
+        <v>0</v>
+      </c>
+      <c r="K69" s="4">
+        <v>0</v>
+      </c>
+      <c r="L69" s="4">
+        <v>5</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" s="4"/>
+    </row>
+    <row r="70" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="1"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="4"/>
+    </row>
+    <row r="71" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C71" s="1">
+        <v>1035</v>
+      </c>
+      <c r="D71" s="1">
+        <v>5</v>
+      </c>
+      <c r="E71" s="4">
+        <v>4032</v>
+      </c>
+      <c r="F71" s="4">
+        <v>150</v>
+      </c>
+      <c r="G71" s="4">
         <v>50</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H71" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I71" s="4">
+        <v>10</v>
+      </c>
+      <c r="J71" s="4">
+        <v>0</v>
+      </c>
+      <c r="K71" s="4">
+        <v>0</v>
+      </c>
+      <c r="L71" s="4">
+        <v>999</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" s="4"/>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C72" s="1">
+        <v>1036</v>
+      </c>
+      <c r="D72" s="1">
+        <v>5</v>
+      </c>
+      <c r="E72" s="4">
+        <v>61000033</v>
+      </c>
+      <c r="F72" s="4">
+        <v>2</v>
+      </c>
+      <c r="G72" s="4">
+        <v>50</v>
+      </c>
+      <c r="H72" s="4">
         <v>400</v>
       </c>
-      <c r="I49" s="4">
-        <v>10</v>
-      </c>
-      <c r="J49" s="4">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4">
-        <v>0</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="4"/>
-    </row>
-    <row r="50" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C50" s="1">
-        <v>1029</v>
-      </c>
-      <c r="D50" s="1">
-        <v>4</v>
-      </c>
-      <c r="E50" s="4">
-        <v>61000027</v>
-      </c>
-      <c r="F50" s="4">
-        <v>3</v>
-      </c>
-      <c r="G50" s="4">
+      <c r="I72" s="4">
+        <v>10</v>
+      </c>
+      <c r="J72" s="4">
+        <v>0</v>
+      </c>
+      <c r="K72" s="4">
+        <v>0</v>
+      </c>
+      <c r="L72" s="4">
+        <v>5</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P72" s="4"/>
+    </row>
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C73" s="1">
+        <v>1037</v>
+      </c>
+      <c r="D73" s="1">
+        <v>5</v>
+      </c>
+      <c r="E73" s="4">
+        <v>61000034</v>
+      </c>
+      <c r="F73" s="4">
+        <v>2</v>
+      </c>
+      <c r="G73" s="4">
+        <v>50</v>
+      </c>
+      <c r="H73" s="4">
+        <v>400</v>
+      </c>
+      <c r="I73" s="4">
+        <v>10</v>
+      </c>
+      <c r="J73" s="4">
+        <v>0</v>
+      </c>
+      <c r="K73" s="4">
+        <v>0</v>
+      </c>
+      <c r="L73" s="4">
+        <v>5</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" s="4"/>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C74" s="1">
+        <v>1038</v>
+      </c>
+      <c r="D74" s="1">
+        <v>5</v>
+      </c>
+      <c r="E74" s="4">
+        <v>61000035</v>
+      </c>
+      <c r="F74" s="4">
+        <v>2</v>
+      </c>
+      <c r="G74" s="4">
         <v>150</v>
       </c>
-      <c r="H50" s="4">
+      <c r="H74" s="4">
         <v>450</v>
       </c>
-      <c r="I50" s="4">
-        <v>10</v>
-      </c>
-      <c r="J50" s="4">
-        <v>0</v>
-      </c>
-      <c r="K50" s="4">
-        <v>0</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="4"/>
-    </row>
-    <row r="51" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C51" s="1">
-        <v>1030</v>
-      </c>
-      <c r="D51" s="1">
-        <v>4</v>
-      </c>
-      <c r="E51" s="4">
-        <v>61000028</v>
-      </c>
-      <c r="F51" s="4">
-        <v>3</v>
-      </c>
-      <c r="G51" s="4">
+      <c r="I74" s="4">
+        <v>10</v>
+      </c>
+      <c r="J74" s="4">
+        <v>0</v>
+      </c>
+      <c r="K74" s="4">
+        <v>0</v>
+      </c>
+      <c r="L74" s="4">
+        <v>5</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P74" s="4"/>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C75" s="1">
+        <v>1039</v>
+      </c>
+      <c r="D75" s="1">
+        <v>5</v>
+      </c>
+      <c r="E75" s="4">
+        <v>61000036</v>
+      </c>
+      <c r="F75" s="4">
+        <v>2</v>
+      </c>
+      <c r="G75" s="4">
         <v>150</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H75" s="4">
         <v>450</v>
       </c>
-      <c r="I51" s="4">
-        <v>10</v>
-      </c>
-      <c r="J51" s="4">
-        <v>0</v>
-      </c>
-      <c r="K51" s="4">
-        <v>0</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="4"/>
-    </row>
-    <row r="52" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C52" s="1">
-        <v>1031</v>
-      </c>
-      <c r="D52" s="1">
-        <v>4</v>
-      </c>
-      <c r="E52" s="4">
-        <v>61000029</v>
-      </c>
-      <c r="F52" s="4">
-        <v>2</v>
-      </c>
-      <c r="G52" s="4">
+      <c r="I75" s="4">
+        <v>10</v>
+      </c>
+      <c r="J75" s="4">
+        <v>0</v>
+      </c>
+      <c r="K75" s="4">
+        <v>0</v>
+      </c>
+      <c r="L75" s="4">
+        <v>5</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P75" s="4"/>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C76" s="1">
+        <v>1040</v>
+      </c>
+      <c r="D76" s="1">
+        <v>5</v>
+      </c>
+      <c r="E76" s="4">
+        <v>61000037</v>
+      </c>
+      <c r="F76" s="4">
+        <v>2</v>
+      </c>
+      <c r="G76" s="4">
         <v>300</v>
       </c>
-      <c r="H52" s="4">
+      <c r="H76" s="4">
         <v>650</v>
       </c>
-      <c r="I52" s="4">
-        <v>10</v>
-      </c>
-      <c r="J52" s="4">
-        <v>0</v>
-      </c>
-      <c r="K52" s="4">
-        <v>0</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="4"/>
-    </row>
-    <row r="53" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C53" s="1">
-        <v>1032</v>
-      </c>
-      <c r="D53" s="1">
-        <v>4</v>
-      </c>
-      <c r="E53" s="4">
-        <v>61000030</v>
-      </c>
-      <c r="F53" s="4">
-        <v>2</v>
-      </c>
-      <c r="G53" s="4">
+      <c r="I76" s="4">
+        <v>10</v>
+      </c>
+      <c r="J76" s="4">
+        <v>0</v>
+      </c>
+      <c r="K76" s="4">
+        <v>0</v>
+      </c>
+      <c r="L76" s="4">
+        <v>5</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" s="4"/>
+    </row>
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C77" s="1">
+        <v>1041</v>
+      </c>
+      <c r="D77" s="1">
+        <v>5</v>
+      </c>
+      <c r="E77" s="4">
+        <v>61000038</v>
+      </c>
+      <c r="F77" s="4">
+        <v>2</v>
+      </c>
+      <c r="G77" s="4">
         <v>300</v>
       </c>
-      <c r="H53" s="4">
+      <c r="H77" s="4">
         <v>650</v>
       </c>
-      <c r="I53" s="4">
-        <v>10</v>
-      </c>
-      <c r="J53" s="4">
-        <v>0</v>
-      </c>
-      <c r="K53" s="4">
-        <v>0</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="4"/>
-    </row>
-    <row r="54" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C54" s="1">
-        <v>1033</v>
-      </c>
-      <c r="D54" s="1">
-        <v>4</v>
-      </c>
-      <c r="E54" s="4">
-        <v>61000031</v>
-      </c>
-      <c r="F54" s="4">
-        <v>2</v>
-      </c>
-      <c r="G54" s="4">
+      <c r="I77" s="4">
+        <v>10</v>
+      </c>
+      <c r="J77" s="4">
+        <v>0</v>
+      </c>
+      <c r="K77" s="4">
+        <v>0</v>
+      </c>
+      <c r="L77" s="4">
+        <v>5</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" s="4"/>
+    </row>
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C78" s="1">
+        <v>1042</v>
+      </c>
+      <c r="D78" s="1">
+        <v>5</v>
+      </c>
+      <c r="E78" s="4">
+        <v>61000039</v>
+      </c>
+      <c r="F78" s="4">
+        <v>2</v>
+      </c>
+      <c r="G78" s="4">
         <v>400</v>
       </c>
-      <c r="H54" s="4">
+      <c r="H78" s="4">
         <v>1000</v>
       </c>
-      <c r="I54" s="4">
-        <v>10</v>
-      </c>
-      <c r="J54" s="4">
-        <v>0</v>
-      </c>
-      <c r="K54" s="4">
-        <v>0</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="4"/>
-    </row>
-    <row r="55" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C55" s="1">
-        <v>1034</v>
-      </c>
-      <c r="D55" s="1">
-        <v>4</v>
-      </c>
-      <c r="E55" s="4">
-        <v>61000032</v>
-      </c>
-      <c r="F55" s="4">
-        <v>2</v>
-      </c>
-      <c r="G55" s="4">
+      <c r="I78" s="4">
+        <v>10</v>
+      </c>
+      <c r="J78" s="4">
+        <v>0</v>
+      </c>
+      <c r="K78" s="4">
+        <v>0</v>
+      </c>
+      <c r="L78" s="4">
+        <v>5</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N78" s="1"/>
+      <c r="O78" s="2"/>
+      <c r="P78" s="4"/>
+    </row>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C79" s="1">
+        <v>1043</v>
+      </c>
+      <c r="D79" s="1">
+        <v>5</v>
+      </c>
+      <c r="E79" s="4">
+        <v>61000040</v>
+      </c>
+      <c r="F79" s="4">
+        <v>2</v>
+      </c>
+      <c r="G79" s="4">
         <v>400</v>
       </c>
-      <c r="H55" s="4">
+      <c r="H79" s="4">
         <v>1000</v>
       </c>
-      <c r="I55" s="4">
-        <v>10</v>
-      </c>
-      <c r="J55" s="4">
-        <v>0</v>
-      </c>
-      <c r="K55" s="4">
-        <v>0</v>
-      </c>
-      <c r="L55" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="4"/>
-    </row>
-    <row r="56" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="1"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="4"/>
-    </row>
-    <row r="57" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C57" s="1">
-        <v>1035</v>
-      </c>
-      <c r="D57" s="1">
-        <v>5</v>
-      </c>
-      <c r="E57" s="4">
-        <v>4032</v>
-      </c>
-      <c r="F57" s="4">
+      <c r="I79" s="4">
+        <v>10</v>
+      </c>
+      <c r="J79" s="4">
+        <v>0</v>
+      </c>
+      <c r="K79" s="4">
+        <v>0</v>
+      </c>
+      <c r="L79" s="4">
+        <v>5</v>
+      </c>
+      <c r="M79" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" s="4"/>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O80" s="2"/>
+      <c r="P80" s="4"/>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C81" s="1">
+        <v>1044</v>
+      </c>
+      <c r="D81" s="1">
+        <v>6</v>
+      </c>
+      <c r="E81" s="4">
+        <v>4055</v>
+      </c>
+      <c r="F81" s="4">
+        <v>200</v>
+      </c>
+      <c r="G81" s="4">
+        <v>50</v>
+      </c>
+      <c r="H81" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I81" s="4">
+        <v>10</v>
+      </c>
+      <c r="J81" s="4">
+        <v>0</v>
+      </c>
+      <c r="K81" s="4">
+        <v>0</v>
+      </c>
+      <c r="L81" s="4">
+        <v>999</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" s="4"/>
+    </row>
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C82" s="1">
+        <v>1045</v>
+      </c>
+      <c r="D82" s="1">
+        <v>6</v>
+      </c>
+      <c r="E82" s="4">
+        <v>61000041</v>
+      </c>
+      <c r="F82" s="4">
+        <v>2</v>
+      </c>
+      <c r="G82" s="4">
+        <v>50</v>
+      </c>
+      <c r="H82" s="4">
+        <v>400</v>
+      </c>
+      <c r="I82" s="4">
+        <v>10</v>
+      </c>
+      <c r="J82" s="4">
+        <v>0</v>
+      </c>
+      <c r="K82" s="4">
+        <v>0</v>
+      </c>
+      <c r="L82" s="4">
+        <v>2</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" s="4"/>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C83" s="1">
+        <v>1046</v>
+      </c>
+      <c r="D83" s="1">
+        <v>6</v>
+      </c>
+      <c r="E83" s="4">
+        <v>61000042</v>
+      </c>
+      <c r="F83" s="4">
+        <v>2</v>
+      </c>
+      <c r="G83" s="4">
+        <v>50</v>
+      </c>
+      <c r="H83" s="4">
+        <v>400</v>
+      </c>
+      <c r="I83" s="4">
+        <v>10</v>
+      </c>
+      <c r="J83" s="4">
+        <v>0</v>
+      </c>
+      <c r="K83" s="4">
+        <v>0</v>
+      </c>
+      <c r="L83" s="4">
+        <v>2</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" s="4"/>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C84" s="1">
+        <v>1047</v>
+      </c>
+      <c r="D84" s="1">
+        <v>6</v>
+      </c>
+      <c r="E84" s="4">
+        <v>61000043</v>
+      </c>
+      <c r="F84" s="4">
+        <v>2</v>
+      </c>
+      <c r="G84" s="4">
         <v>150</v>
       </c>
-      <c r="G57" s="4">
-        <v>50</v>
-      </c>
-      <c r="H57" s="4">
+      <c r="H84" s="4">
+        <v>450</v>
+      </c>
+      <c r="I84" s="4">
+        <v>10</v>
+      </c>
+      <c r="J84" s="4">
+        <v>0</v>
+      </c>
+      <c r="K84" s="4">
+        <v>0</v>
+      </c>
+      <c r="L84" s="4">
+        <v>2</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O84" s="2"/>
+      <c r="P84" s="4"/>
+    </row>
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C85" s="1">
+        <v>1048</v>
+      </c>
+      <c r="D85" s="1">
+        <v>6</v>
+      </c>
+      <c r="E85" s="4">
+        <v>61000044</v>
+      </c>
+      <c r="F85" s="4">
+        <v>2</v>
+      </c>
+      <c r="G85" s="4">
+        <v>150</v>
+      </c>
+      <c r="H85" s="4">
+        <v>450</v>
+      </c>
+      <c r="I85" s="4">
+        <v>10</v>
+      </c>
+      <c r="J85" s="4">
+        <v>0</v>
+      </c>
+      <c r="K85" s="4">
+        <v>0</v>
+      </c>
+      <c r="L85" s="4">
+        <v>2</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" s="4"/>
+    </row>
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C86" s="1">
+        <v>1049</v>
+      </c>
+      <c r="D86" s="1">
+        <v>6</v>
+      </c>
+      <c r="E86" s="4">
+        <v>61000045</v>
+      </c>
+      <c r="F86" s="4">
+        <v>2</v>
+      </c>
+      <c r="G86" s="4">
+        <v>300</v>
+      </c>
+      <c r="H86" s="4">
+        <v>650</v>
+      </c>
+      <c r="I86" s="4">
+        <v>10</v>
+      </c>
+      <c r="J86" s="4">
+        <v>0</v>
+      </c>
+      <c r="K86" s="4">
+        <v>0</v>
+      </c>
+      <c r="L86" s="4">
+        <v>2</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" s="4"/>
+    </row>
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C87" s="1">
+        <v>1050</v>
+      </c>
+      <c r="D87" s="1">
+        <v>6</v>
+      </c>
+      <c r="E87" s="4">
+        <v>61000046</v>
+      </c>
+      <c r="F87" s="4">
+        <v>2</v>
+      </c>
+      <c r="G87" s="4">
+        <v>300</v>
+      </c>
+      <c r="H87" s="4">
+        <v>650</v>
+      </c>
+      <c r="I87" s="4">
+        <v>10</v>
+      </c>
+      <c r="J87" s="4">
+        <v>0</v>
+      </c>
+      <c r="K87" s="4">
+        <v>0</v>
+      </c>
+      <c r="L87" s="4">
+        <v>2</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" s="4"/>
+    </row>
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C88" s="1">
+        <v>1051</v>
+      </c>
+      <c r="D88" s="1">
+        <v>6</v>
+      </c>
+      <c r="E88" s="4">
+        <v>61000047</v>
+      </c>
+      <c r="F88" s="4">
+        <v>2</v>
+      </c>
+      <c r="G88" s="4">
+        <v>400</v>
+      </c>
+      <c r="H88" s="4">
         <v>1000</v>
       </c>
-      <c r="I57" s="4">
-        <v>10</v>
-      </c>
-      <c r="J57" s="4">
-        <v>0</v>
-      </c>
-      <c r="K57" s="4">
-        <v>0</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="4"/>
-    </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C58" s="1">
-        <v>1036</v>
-      </c>
-      <c r="D58" s="1">
-        <v>5</v>
-      </c>
-      <c r="E58" s="4">
-        <v>61000033</v>
-      </c>
-      <c r="F58" s="4">
-        <v>2</v>
-      </c>
-      <c r="G58" s="4">
-        <v>50</v>
-      </c>
-      <c r="H58" s="4">
+      <c r="I88" s="4">
+        <v>10</v>
+      </c>
+      <c r="J88" s="4">
+        <v>0</v>
+      </c>
+      <c r="K88" s="4">
+        <v>0</v>
+      </c>
+      <c r="L88" s="4">
+        <v>2</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" s="4"/>
+    </row>
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C89" s="1">
+        <v>1052</v>
+      </c>
+      <c r="D89" s="1">
+        <v>6</v>
+      </c>
+      <c r="E89" s="4">
+        <v>61000048</v>
+      </c>
+      <c r="F89" s="4">
+        <v>2</v>
+      </c>
+      <c r="G89" s="4">
         <v>400</v>
       </c>
-      <c r="I58" s="4">
-        <v>10</v>
-      </c>
-      <c r="J58" s="4">
-        <v>0</v>
-      </c>
-      <c r="K58" s="4">
-        <v>0</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O58" s="4"/>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C59" s="1">
-        <v>1037</v>
-      </c>
-      <c r="D59" s="1">
-        <v>5</v>
-      </c>
-      <c r="E59" s="4">
-        <v>61000034</v>
-      </c>
-      <c r="F59" s="4">
-        <v>2</v>
-      </c>
-      <c r="G59" s="4">
-        <v>50</v>
-      </c>
-      <c r="H59" s="4">
-        <v>400</v>
-      </c>
-      <c r="I59" s="4">
-        <v>10</v>
-      </c>
-      <c r="J59" s="4">
-        <v>0</v>
-      </c>
-      <c r="K59" s="4">
-        <v>0</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="4"/>
-    </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C60" s="1">
-        <v>1038</v>
-      </c>
-      <c r="D60" s="1">
-        <v>5</v>
-      </c>
-      <c r="E60" s="4">
-        <v>61000035</v>
-      </c>
-      <c r="F60" s="4">
-        <v>2</v>
-      </c>
-      <c r="G60" s="4">
-        <v>150</v>
-      </c>
-      <c r="H60" s="4">
-        <v>450</v>
-      </c>
-      <c r="I60" s="4">
-        <v>10</v>
-      </c>
-      <c r="J60" s="4">
-        <v>0</v>
-      </c>
-      <c r="K60" s="4">
-        <v>0</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="O60" s="4"/>
-    </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C61" s="1">
-        <v>1039</v>
-      </c>
-      <c r="D61" s="1">
-        <v>5</v>
-      </c>
-      <c r="E61" s="4">
-        <v>61000036</v>
-      </c>
-      <c r="F61" s="4">
-        <v>2</v>
-      </c>
-      <c r="G61" s="4">
-        <v>150</v>
-      </c>
-      <c r="H61" s="4">
-        <v>450</v>
-      </c>
-      <c r="I61" s="4">
-        <v>10</v>
-      </c>
-      <c r="J61" s="4">
-        <v>0</v>
-      </c>
-      <c r="K61" s="4">
-        <v>0</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O61" s="4"/>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C62" s="1">
-        <v>1040</v>
-      </c>
-      <c r="D62" s="1">
-        <v>5</v>
-      </c>
-      <c r="E62" s="4">
-        <v>61000037</v>
-      </c>
-      <c r="F62" s="4">
-        <v>2</v>
-      </c>
-      <c r="G62" s="4">
-        <v>300</v>
-      </c>
-      <c r="H62" s="4">
-        <v>650</v>
-      </c>
-      <c r="I62" s="4">
-        <v>10</v>
-      </c>
-      <c r="J62" s="4">
-        <v>0</v>
-      </c>
-      <c r="K62" s="4">
-        <v>0</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="4"/>
-    </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C63" s="1">
-        <v>1041</v>
-      </c>
-      <c r="D63" s="1">
-        <v>5</v>
-      </c>
-      <c r="E63" s="4">
-        <v>61000038</v>
-      </c>
-      <c r="F63" s="4">
-        <v>2</v>
-      </c>
-      <c r="G63" s="4">
-        <v>300</v>
-      </c>
-      <c r="H63" s="4">
-        <v>650</v>
-      </c>
-      <c r="I63" s="4">
-        <v>10</v>
-      </c>
-      <c r="J63" s="4">
-        <v>0</v>
-      </c>
-      <c r="K63" s="4">
-        <v>0</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="4"/>
-    </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C64" s="1">
-        <v>1042</v>
-      </c>
-      <c r="D64" s="1">
-        <v>5</v>
-      </c>
-      <c r="E64" s="4">
-        <v>61000039</v>
-      </c>
-      <c r="F64" s="4">
-        <v>2</v>
-      </c>
-      <c r="G64" s="4">
-        <v>400</v>
-      </c>
-      <c r="H64" s="4">
+      <c r="H89" s="4">
         <v>1000</v>
       </c>
-      <c r="I64" s="4">
-        <v>10</v>
-      </c>
-      <c r="J64" s="4">
-        <v>0</v>
-      </c>
-      <c r="K64" s="4">
-        <v>0</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="M64" s="1"/>
-      <c r="N64" s="2"/>
-      <c r="O64" s="4"/>
-    </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C65" s="1">
-        <v>1043</v>
-      </c>
-      <c r="D65" s="1">
-        <v>5</v>
-      </c>
-      <c r="E65" s="4">
-        <v>61000040</v>
-      </c>
-      <c r="F65" s="4">
-        <v>2</v>
-      </c>
-      <c r="G65" s="4">
-        <v>400</v>
-      </c>
-      <c r="H65" s="4">
-        <v>1000</v>
-      </c>
-      <c r="I65" s="4">
-        <v>10</v>
-      </c>
-      <c r="J65" s="4">
-        <v>0</v>
-      </c>
-      <c r="K65" s="4">
-        <v>0</v>
-      </c>
-      <c r="L65" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="4"/>
-    </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N66" s="2"/>
-      <c r="O66" s="4"/>
-    </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N67" s="2"/>
-      <c r="O67" s="4"/>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N68" s="2"/>
-      <c r="O68" s="4"/>
-    </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N69" s="2"/>
-      <c r="O69" s="4"/>
-    </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N70" s="2"/>
-      <c r="O70" s="4"/>
-    </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N71" s="2"/>
-      <c r="O71" s="4"/>
-    </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N72" s="2"/>
-      <c r="O72" s="4"/>
-    </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N73" s="2"/>
-      <c r="O73" s="4"/>
-    </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N74" s="2"/>
-      <c r="O74" s="4"/>
-    </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N75" s="2"/>
-      <c r="O75" s="4"/>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N76" s="2"/>
-      <c r="O76" s="4"/>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N77" s="2"/>
-      <c r="O77" s="4"/>
-    </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N78" s="2"/>
-      <c r="O78" s="4"/>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N79" s="2"/>
-      <c r="O79" s="4"/>
-    </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="N80" s="2"/>
-      <c r="O80" s="4"/>
-    </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N81" s="2"/>
-      <c r="O81" s="4"/>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N82" s="2"/>
-      <c r="O82" s="4"/>
-    </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N83" s="2"/>
-      <c r="O83" s="4"/>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N84" s="2"/>
-      <c r="O84" s="4"/>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N85" s="2"/>
-      <c r="O85" s="4"/>
-    </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N86" s="2"/>
-      <c r="O86" s="4"/>
-    </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N87" s="2"/>
-      <c r="O87" s="4"/>
-    </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N88" s="2"/>
-      <c r="O88" s="4"/>
-    </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N89" s="2"/>
-      <c r="O89" s="4"/>
-    </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N90" s="2"/>
-      <c r="O90" s="4"/>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N91" s="2"/>
-      <c r="O91" s="4"/>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N92" s="2"/>
-      <c r="O92" s="4"/>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N93" s="2"/>
-      <c r="O93" s="4"/>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N94" s="2"/>
-      <c r="O94" s="4"/>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N95" s="2"/>
-      <c r="O95" s="4"/>
-    </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="14:15">
-      <c r="N96" s="2"/>
-      <c r="O96" s="4"/>
+      <c r="I89" s="4">
+        <v>10</v>
+      </c>
+      <c r="J89" s="4">
+        <v>0</v>
+      </c>
+      <c r="K89" s="4">
+        <v>0</v>
+      </c>
+      <c r="L89" s="4">
+        <v>2</v>
+      </c>
+      <c r="M89" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" s="4"/>
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O90" s="2"/>
+      <c r="P90" s="4"/>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O91" s="2"/>
+      <c r="P91" s="4"/>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O92" s="2"/>
+      <c r="P92" s="4"/>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O93" s="2"/>
+      <c r="P93" s="4"/>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O94" s="2"/>
+      <c r="P94" s="4"/>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O95" s="2"/>
+      <c r="P95" s="4"/>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O96" s="2"/>
+      <c r="P96" s="4"/>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O97" s="2"/>
+      <c r="P97" s="4"/>
+    </row>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O98" s="2"/>
+      <c r="P98" s="4"/>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O99" s="2"/>
+      <c r="P99" s="4"/>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O100" s="2"/>
+      <c r="P100" s="4"/>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O101" s="2"/>
+      <c r="P101" s="4"/>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O102" s="2"/>
+      <c r="P102" s="4"/>
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O103" s="2"/>
+      <c r="P103" s="4"/>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O104" s="2"/>
+      <c r="P104" s="4"/>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O105" s="2"/>
+      <c r="P105" s="4"/>
+    </row>
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O106" s="2"/>
+      <c r="P106" s="4"/>
+    </row>
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O107" s="2"/>
+      <c r="P107" s="4"/>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O108" s="2"/>
+      <c r="P108" s="4"/>
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O109" s="2"/>
+      <c r="P109" s="4"/>
+    </row>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="15:16">
+      <c r="O110" s="2"/>
+      <c r="P110" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="90">
   <si>
     <t>#</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>ExcludeLevel</t>
-  </si>
-  <si>
-    <t>Max</t>
   </si>
   <si>
     <t>Name</t>
@@ -1320,26 +1317,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P110"/>
+  <dimension ref="C1:O110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="12" width="14.4166666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.25" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="5" max="11" width="14.4166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.25" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1370,11 +1367,8 @@
       <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1405,46 +1399,40 @@
       <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="3" t="s">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:16">
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1472,17 +1460,14 @@
       <c r="K6" s="4">
         <v>10</v>
       </c>
-      <c r="L6" s="4">
-        <v>999</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="L6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="2"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="4"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1510,17 +1495,14 @@
       <c r="K7" s="4">
         <v>10</v>
       </c>
-      <c r="L7" s="4">
-        <v>999</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="L7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1548,17 +1530,14 @@
       <c r="K8" s="4">
         <v>10</v>
       </c>
-      <c r="L8" s="4">
-        <v>999</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N8" s="1"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="4"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:16">
+      <c r="L8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:15">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1586,17 +1565,14 @@
       <c r="K9" s="4">
         <v>10</v>
       </c>
-      <c r="L9" s="4">
-        <v>999</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N9" s="1"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="4"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1624,17 +1600,14 @@
       <c r="K10" s="4">
         <v>10</v>
       </c>
-      <c r="L10" s="4">
-        <v>999</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="1"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="4"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1662,17 +1635,14 @@
       <c r="K11" s="4">
         <v>10</v>
       </c>
-      <c r="L11" s="4">
-        <v>999</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N11" s="1"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="4"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1700,17 +1670,14 @@
       <c r="K12" s="4">
         <v>10</v>
       </c>
-      <c r="L12" s="4">
-        <v>999</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N12" s="1"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="4"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1738,17 +1705,14 @@
       <c r="K13" s="4">
         <v>10</v>
       </c>
-      <c r="L13" s="4">
-        <v>999</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="1"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="4"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1776,17 +1740,14 @@
       <c r="K14" s="4">
         <v>10</v>
       </c>
-      <c r="L14" s="4">
-        <v>999</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="1"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="4"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="1"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1814,17 +1775,14 @@
       <c r="K15" s="4">
         <v>10</v>
       </c>
-      <c r="L15" s="4">
-        <v>999</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N15" s="1"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="4"/>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="1"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="3:15">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="4"/>
@@ -1834,12 +1792,11 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="1"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="4"/>
-    </row>
-    <row r="17" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L16" s="1"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="3:15">
       <c r="C17" s="2">
         <v>11</v>
       </c>
@@ -1867,16 +1824,13 @@
       <c r="K17" s="4">
         <v>10</v>
       </c>
-      <c r="L17" s="4">
-        <v>999</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O17" s="2"/>
-      <c r="P17" s="4"/>
-    </row>
-    <row r="18" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" customFormat="1" customHeight="1" spans="3:15">
       <c r="C18" s="2">
         <v>12</v>
       </c>
@@ -1904,16 +1858,13 @@
       <c r="K18" s="4">
         <v>10</v>
       </c>
-      <c r="L18" s="4">
-        <v>999</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18" s="2"/>
-      <c r="P18" s="4"/>
-    </row>
-    <row r="19" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" customFormat="1" customHeight="1" spans="3:15">
       <c r="C19" s="2">
         <v>13</v>
       </c>
@@ -1941,16 +1892,13 @@
       <c r="K19" s="4">
         <v>10</v>
       </c>
-      <c r="L19" s="4">
-        <v>999</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" s="2"/>
-      <c r="P19" s="4"/>
-    </row>
-    <row r="20" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" customFormat="1" customHeight="1" spans="3:15">
       <c r="C20" s="2">
         <v>14</v>
       </c>
@@ -1978,16 +1926,13 @@
       <c r="K20" s="4">
         <v>10</v>
       </c>
-      <c r="L20" s="4">
-        <v>999</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="2"/>
-      <c r="P20" s="4"/>
-    </row>
-    <row r="21" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" customFormat="1" customHeight="1" spans="3:15">
       <c r="C21" s="2">
         <v>15</v>
       </c>
@@ -2015,16 +1960,13 @@
       <c r="K21" s="4">
         <v>10</v>
       </c>
-      <c r="L21" s="4">
-        <v>999</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O21" s="2"/>
-      <c r="P21" s="4"/>
-    </row>
-    <row r="22" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" customFormat="1" customHeight="1" spans="3:15">
       <c r="C22" s="2">
         <v>16</v>
       </c>
@@ -2052,16 +1994,13 @@
       <c r="K22" s="4">
         <v>10</v>
       </c>
-      <c r="L22" s="4">
-        <v>999</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O22" s="2"/>
-      <c r="P22" s="4"/>
-    </row>
-    <row r="23" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" customFormat="1" customHeight="1" spans="3:15">
       <c r="C23" s="2">
         <v>17</v>
       </c>
@@ -2089,16 +2028,13 @@
       <c r="K23" s="4">
         <v>10</v>
       </c>
-      <c r="L23" s="4">
-        <v>999</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O23" s="2"/>
-      <c r="P23" s="4"/>
-    </row>
-    <row r="24" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" customFormat="1" customHeight="1" spans="3:15">
       <c r="C24" s="2">
         <v>18</v>
       </c>
@@ -2126,16 +2062,13 @@
       <c r="K24" s="4">
         <v>10</v>
       </c>
-      <c r="L24" s="4">
-        <v>999</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="O24" s="2"/>
-      <c r="P24" s="4"/>
-    </row>
-    <row r="25" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L24" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="3:15">
       <c r="C25" s="2">
         <v>19</v>
       </c>
@@ -2163,16 +2096,13 @@
       <c r="K25" s="4">
         <v>10</v>
       </c>
-      <c r="L25" s="4">
-        <v>999</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O25" s="2"/>
-      <c r="P25" s="4"/>
-    </row>
-    <row r="26" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="3:15">
       <c r="C26" s="2">
         <v>20</v>
       </c>
@@ -2200,16 +2130,13 @@
       <c r="K26" s="4">
         <v>10</v>
       </c>
-      <c r="L26" s="4">
-        <v>999</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O26" s="2"/>
-      <c r="P26" s="4"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="3:15">
       <c r="C27" s="2">
         <v>21</v>
       </c>
@@ -2237,16 +2164,13 @@
       <c r="K27" s="4">
         <v>10</v>
       </c>
-      <c r="L27" s="4">
-        <v>999</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="O27" s="2"/>
-      <c r="P27" s="4"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="4"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="3:15">
       <c r="C28" s="2">
         <v>22</v>
       </c>
@@ -2274,16 +2198,13 @@
       <c r="K28" s="4">
         <v>10</v>
       </c>
-      <c r="L28" s="4">
-        <v>999</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O28" s="2"/>
-      <c r="P28" s="4"/>
-    </row>
-    <row r="29" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="4"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="3:15">
       <c r="C29" s="2">
         <v>23</v>
       </c>
@@ -2311,16 +2232,13 @@
       <c r="K29" s="4">
         <v>10</v>
       </c>
-      <c r="L29" s="4">
-        <v>999</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O29" s="2"/>
-      <c r="P29" s="4"/>
-    </row>
-    <row r="30" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="3:15">
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="4"/>
@@ -2330,12 +2248,11 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="1"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="4"/>
-    </row>
-    <row r="31" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L30" s="1"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="3:15">
       <c r="C31" s="1">
         <v>999</v>
       </c>
@@ -2363,16 +2280,13 @@
       <c r="K31" s="4">
         <v>0</v>
       </c>
-      <c r="L31" s="4">
-        <v>999</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O31" s="2"/>
-      <c r="P31" s="4"/>
-    </row>
-    <row r="32" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="3:15">
       <c r="C32" s="2">
         <v>1000</v>
       </c>
@@ -2400,16 +2314,13 @@
       <c r="K32" s="4">
         <v>0</v>
       </c>
-      <c r="L32" s="4">
-        <v>5</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O32" s="2"/>
-      <c r="P32" s="4"/>
-    </row>
-    <row r="33" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:15">
       <c r="C33" s="2">
         <v>1001</v>
       </c>
@@ -2437,16 +2348,13 @@
       <c r="K33" s="4">
         <v>0</v>
       </c>
-      <c r="L33" s="4">
-        <v>5</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O33" s="2"/>
-      <c r="P33" s="4"/>
-    </row>
-    <row r="34" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="3:15">
       <c r="C34" s="2">
         <v>1002</v>
       </c>
@@ -2474,16 +2382,13 @@
       <c r="K34" s="4">
         <v>0</v>
       </c>
-      <c r="L34" s="4">
-        <v>5</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O34" s="2"/>
-      <c r="P34" s="4"/>
-    </row>
-    <row r="35" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="3:15">
       <c r="C35" s="2">
         <v>1003</v>
       </c>
@@ -2511,16 +2416,13 @@
       <c r="K35" s="4">
         <v>0</v>
       </c>
-      <c r="L35" s="4">
-        <v>5</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O35" s="2"/>
-      <c r="P35" s="4"/>
-    </row>
-    <row r="36" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="4"/>
+    </row>
+    <row r="36" customFormat="1" customHeight="1" spans="3:15">
       <c r="C36" s="2">
         <v>1004</v>
       </c>
@@ -2548,16 +2450,13 @@
       <c r="K36" s="4">
         <v>0</v>
       </c>
-      <c r="L36" s="4">
-        <v>5</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O36" s="2"/>
-      <c r="P36" s="4"/>
-    </row>
-    <row r="37" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" customFormat="1" customHeight="1" spans="3:15">
       <c r="C37" s="2">
         <v>1005</v>
       </c>
@@ -2585,16 +2484,13 @@
       <c r="K37" s="4">
         <v>0</v>
       </c>
-      <c r="L37" s="4">
-        <v>5</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O37" s="2"/>
-      <c r="P37" s="4"/>
-    </row>
-    <row r="38" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" customFormat="1" customHeight="1" spans="3:15">
       <c r="C38" s="2">
         <v>1006</v>
       </c>
@@ -2622,16 +2518,13 @@
       <c r="K38" s="4">
         <v>0</v>
       </c>
-      <c r="L38" s="4">
-        <v>5</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O38" s="2"/>
-      <c r="P38" s="4"/>
-    </row>
-    <row r="39" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="3:15">
       <c r="C39" s="2">
         <v>1007</v>
       </c>
@@ -2659,16 +2552,13 @@
       <c r="K39" s="4">
         <v>0</v>
       </c>
-      <c r="L39" s="4">
-        <v>5</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O39" s="2"/>
-      <c r="P39" s="4"/>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L39" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="4"/>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:15">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="4"/>
@@ -2678,12 +2568,11 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="1"/>
-      <c r="O40" s="2"/>
-      <c r="P40" s="4"/>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L40" s="1"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="4"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="3:15">
       <c r="C41" s="1">
         <v>1008</v>
       </c>
@@ -2711,16 +2600,13 @@
       <c r="K41" s="4">
         <v>0</v>
       </c>
-      <c r="L41" s="4">
-        <v>999</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O41" s="2"/>
-      <c r="P41" s="4"/>
-    </row>
-    <row r="42" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="3:15">
       <c r="C42" s="1">
         <v>1009</v>
       </c>
@@ -2748,16 +2634,13 @@
       <c r="K42" s="4">
         <v>0</v>
       </c>
-      <c r="L42" s="4">
-        <v>5</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="O42" s="2"/>
-      <c r="P42" s="4"/>
-    </row>
-    <row r="43" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="3:15">
       <c r="C43" s="1">
         <v>1010</v>
       </c>
@@ -2785,16 +2668,13 @@
       <c r="K43" s="4">
         <v>0</v>
       </c>
-      <c r="L43" s="4">
-        <v>5</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O43" s="2"/>
-      <c r="P43" s="4"/>
-    </row>
-    <row r="44" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="4"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="3:15">
       <c r="C44" s="1">
         <v>1011</v>
       </c>
@@ -2822,16 +2702,13 @@
       <c r="K44" s="4">
         <v>0</v>
       </c>
-      <c r="L44" s="4">
-        <v>5</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O44" s="2"/>
-      <c r="P44" s="4"/>
-    </row>
-    <row r="45" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="3:15">
       <c r="C45" s="1">
         <v>1012</v>
       </c>
@@ -2859,16 +2736,13 @@
       <c r="K45" s="4">
         <v>0</v>
       </c>
-      <c r="L45" s="4">
-        <v>5</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O45" s="2"/>
-      <c r="P45" s="4"/>
-    </row>
-    <row r="46" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="4"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="3:15">
       <c r="C46" s="1">
         <v>1013</v>
       </c>
@@ -2896,16 +2770,13 @@
       <c r="K46" s="4">
         <v>0</v>
       </c>
-      <c r="L46" s="4">
-        <v>5</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O46" s="2"/>
-      <c r="P46" s="4"/>
-    </row>
-    <row r="47" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="3:15">
       <c r="C47" s="1">
         <v>1014</v>
       </c>
@@ -2933,16 +2804,13 @@
       <c r="K47" s="4">
         <v>0</v>
       </c>
-      <c r="L47" s="4">
-        <v>5</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O47" s="2"/>
-      <c r="P47" s="4"/>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L47" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="3:15">
       <c r="C48" s="1">
         <v>1015</v>
       </c>
@@ -2970,16 +2838,13 @@
       <c r="K48" s="4">
         <v>0</v>
       </c>
-      <c r="L48" s="4">
-        <v>5</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O48" s="2"/>
-      <c r="P48" s="4"/>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L48" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="4"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:15">
       <c r="C49" s="1">
         <v>1016</v>
       </c>
@@ -3007,16 +2872,13 @@
       <c r="K49" s="4">
         <v>0</v>
       </c>
-      <c r="L49" s="4">
-        <v>5</v>
-      </c>
-      <c r="M49" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="O49" s="2"/>
-      <c r="P49" s="4"/>
-    </row>
-    <row r="50" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L49" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="4"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:15">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="4"/>
@@ -3026,12 +2888,11 @@
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="1"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="4"/>
-    </row>
-    <row r="51" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L50" s="1"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="4"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:15">
       <c r="C51" s="1">
         <v>1017</v>
       </c>
@@ -3059,16 +2920,13 @@
       <c r="K51" s="4">
         <v>0</v>
       </c>
-      <c r="L51" s="4">
-        <v>999</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" s="4"/>
-    </row>
-    <row r="52" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L51" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="4"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:15">
       <c r="C52" s="1">
         <v>1018</v>
       </c>
@@ -3096,16 +2954,13 @@
       <c r="K52" s="4">
         <v>0</v>
       </c>
-      <c r="L52" s="4">
-        <v>5</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" s="4"/>
-    </row>
-    <row r="53" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="4"/>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="3:15">
       <c r="C53" s="1">
         <v>1019</v>
       </c>
@@ -3133,16 +2988,13 @@
       <c r="K53" s="4">
         <v>0</v>
       </c>
-      <c r="L53" s="4">
-        <v>5</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="O53" s="2"/>
-      <c r="P53" s="4"/>
-    </row>
-    <row r="54" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="4"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="3:15">
       <c r="C54" s="1">
         <v>1020</v>
       </c>
@@ -3170,16 +3022,13 @@
       <c r="K54" s="4">
         <v>0</v>
       </c>
-      <c r="L54" s="4">
-        <v>5</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" s="4"/>
-    </row>
-    <row r="55" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="4"/>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="3:15">
       <c r="C55" s="1">
         <v>1021</v>
       </c>
@@ -3207,16 +3056,13 @@
       <c r="K55" s="4">
         <v>0</v>
       </c>
-      <c r="L55" s="4">
-        <v>5</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O55" s="2"/>
-      <c r="P55" s="4"/>
-    </row>
-    <row r="56" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L55" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="4"/>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="3:15">
       <c r="C56" s="1">
         <v>1022</v>
       </c>
@@ -3244,16 +3090,13 @@
       <c r="K56" s="4">
         <v>0</v>
       </c>
-      <c r="L56" s="4">
-        <v>5</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" s="4"/>
-    </row>
-    <row r="57" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="4"/>
+    </row>
+    <row r="57" customFormat="1" customHeight="1" spans="3:15">
       <c r="C57" s="1">
         <v>1023</v>
       </c>
@@ -3281,16 +3124,13 @@
       <c r="K57" s="4">
         <v>0</v>
       </c>
-      <c r="L57" s="4">
-        <v>5</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="O57" s="2"/>
-      <c r="P57" s="4"/>
-    </row>
-    <row r="58" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L57" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="4"/>
+    </row>
+    <row r="58" customFormat="1" customHeight="1" spans="3:15">
       <c r="C58" s="1">
         <v>1024</v>
       </c>
@@ -3318,16 +3158,13 @@
       <c r="K58" s="4">
         <v>0</v>
       </c>
-      <c r="L58" s="4">
-        <v>5</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" s="4"/>
-    </row>
-    <row r="59" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="4"/>
+    </row>
+    <row r="59" customFormat="1" customHeight="1" spans="3:15">
       <c r="C59" s="1">
         <v>1025</v>
       </c>
@@ -3355,21 +3192,18 @@
       <c r="K59" s="4">
         <v>0</v>
       </c>
-      <c r="L59" s="4">
-        <v>5</v>
-      </c>
-      <c r="M59" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="O59" s="2"/>
-      <c r="P59" s="4"/>
-    </row>
-    <row r="60" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L59" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="4"/>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="3:15">
       <c r="C60" s="1"/>
-      <c r="O60" s="2"/>
-      <c r="P60" s="4"/>
-    </row>
-    <row r="61" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N60" s="2"/>
+      <c r="O60" s="4"/>
+    </row>
+    <row r="61" customFormat="1" customHeight="1" spans="3:15">
       <c r="C61" s="1">
         <v>1026</v>
       </c>
@@ -3397,16 +3231,13 @@
       <c r="K61" s="4">
         <v>0</v>
       </c>
-      <c r="L61" s="4">
-        <v>999</v>
-      </c>
-      <c r="M61" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" s="4"/>
-    </row>
-    <row r="62" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L61" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="4"/>
+    </row>
+    <row r="62" customFormat="1" customHeight="1" spans="3:15">
       <c r="C62" s="1">
         <v>1027</v>
       </c>
@@ -3434,16 +3265,13 @@
       <c r="K62" s="4">
         <v>0</v>
       </c>
-      <c r="L62" s="4">
-        <v>5</v>
-      </c>
-      <c r="M62" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" s="4"/>
-    </row>
-    <row r="63" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L62" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="4"/>
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="3:15">
       <c r="C63" s="1">
         <v>1028</v>
       </c>
@@ -3471,16 +3299,13 @@
       <c r="K63" s="4">
         <v>0</v>
       </c>
-      <c r="L63" s="4">
-        <v>5</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" s="4"/>
-    </row>
-    <row r="64" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L63" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="4"/>
+    </row>
+    <row r="64" customFormat="1" customHeight="1" spans="3:15">
       <c r="C64" s="1">
         <v>1029</v>
       </c>
@@ -3508,16 +3333,13 @@
       <c r="K64" s="4">
         <v>0</v>
       </c>
-      <c r="L64" s="4">
-        <v>5</v>
-      </c>
-      <c r="M64" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" s="4"/>
-    </row>
-    <row r="65" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L64" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="4"/>
+    </row>
+    <row r="65" customFormat="1" customHeight="1" spans="3:15">
       <c r="C65" s="1">
         <v>1030</v>
       </c>
@@ -3545,16 +3367,13 @@
       <c r="K65" s="4">
         <v>0</v>
       </c>
-      <c r="L65" s="4">
-        <v>5</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" s="4"/>
-    </row>
-    <row r="66" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L65" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="4"/>
+    </row>
+    <row r="66" customFormat="1" customHeight="1" spans="3:15">
       <c r="C66" s="1">
         <v>1031</v>
       </c>
@@ -3582,16 +3401,13 @@
       <c r="K66" s="4">
         <v>0</v>
       </c>
-      <c r="L66" s="4">
-        <v>5</v>
-      </c>
-      <c r="M66" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" s="4"/>
-    </row>
-    <row r="67" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L66" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="4"/>
+    </row>
+    <row r="67" customFormat="1" customHeight="1" spans="3:15">
       <c r="C67" s="1">
         <v>1032</v>
       </c>
@@ -3619,16 +3435,13 @@
       <c r="K67" s="4">
         <v>0</v>
       </c>
-      <c r="L67" s="4">
-        <v>5</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" s="4"/>
-    </row>
-    <row r="68" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L67" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="4"/>
+    </row>
+    <row r="68" customFormat="1" customHeight="1" spans="3:15">
       <c r="C68" s="1">
         <v>1033</v>
       </c>
@@ -3656,16 +3469,13 @@
       <c r="K68" s="4">
         <v>0</v>
       </c>
-      <c r="L68" s="4">
-        <v>5</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O68" s="2"/>
-      <c r="P68" s="4"/>
-    </row>
-    <row r="69" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L68" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="4"/>
+    </row>
+    <row r="69" customFormat="1" customHeight="1" spans="3:15">
       <c r="C69" s="1">
         <v>1034</v>
       </c>
@@ -3693,16 +3503,13 @@
       <c r="K69" s="4">
         <v>0</v>
       </c>
-      <c r="L69" s="4">
-        <v>5</v>
-      </c>
-      <c r="M69" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="O69" s="2"/>
-      <c r="P69" s="4"/>
-    </row>
-    <row r="70" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L69" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="4"/>
+    </row>
+    <row r="70" customFormat="1" customHeight="1" spans="3:15">
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="4"/>
@@ -3712,12 +3519,11 @@
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="1"/>
-      <c r="O70" s="2"/>
-      <c r="P70" s="4"/>
-    </row>
-    <row r="71" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L70" s="1"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="4"/>
+    </row>
+    <row r="71" customFormat="1" customHeight="1" spans="3:15">
       <c r="C71" s="1">
         <v>1035</v>
       </c>
@@ -3745,16 +3551,13 @@
       <c r="K71" s="4">
         <v>0</v>
       </c>
-      <c r="L71" s="4">
-        <v>999</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" s="4"/>
-    </row>
-    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L71" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="4"/>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C72" s="1">
         <v>1036</v>
       </c>
@@ -3782,15 +3585,12 @@
       <c r="K72" s="4">
         <v>0</v>
       </c>
-      <c r="L72" s="4">
-        <v>5</v>
-      </c>
-      <c r="M72" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P72" s="4"/>
-    </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O72" s="4"/>
+    </row>
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C73" s="1">
         <v>1037</v>
       </c>
@@ -3818,16 +3618,13 @@
       <c r="K73" s="4">
         <v>0</v>
       </c>
-      <c r="L73" s="4">
-        <v>5</v>
-      </c>
-      <c r="M73" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" s="4"/>
-    </row>
-    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L73" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="4"/>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C74" s="1">
         <v>1038</v>
       </c>
@@ -3855,15 +3652,12 @@
       <c r="K74" s="4">
         <v>0</v>
       </c>
-      <c r="L74" s="4">
-        <v>5</v>
-      </c>
-      <c r="M74" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="P74" s="4"/>
-    </row>
-    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L74" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O74" s="4"/>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C75" s="1">
         <v>1039</v>
       </c>
@@ -3891,15 +3685,12 @@
       <c r="K75" s="4">
         <v>0</v>
       </c>
-      <c r="L75" s="4">
-        <v>5</v>
-      </c>
-      <c r="M75" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="P75" s="4"/>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L75" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O75" s="4"/>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C76" s="1">
         <v>1040</v>
       </c>
@@ -3927,16 +3718,13 @@
       <c r="K76" s="4">
         <v>0</v>
       </c>
-      <c r="L76" s="4">
-        <v>5</v>
-      </c>
-      <c r="M76" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O76" s="2"/>
-      <c r="P76" s="4"/>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L76" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="4"/>
+    </row>
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C77" s="1">
         <v>1041</v>
       </c>
@@ -3964,16 +3752,13 @@
       <c r="K77" s="4">
         <v>0</v>
       </c>
-      <c r="L77" s="4">
-        <v>5</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" s="4"/>
-    </row>
-    <row r="78" s="2" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L77" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="4"/>
+    </row>
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C78" s="1">
         <v>1042</v>
       </c>
@@ -4001,17 +3786,14 @@
       <c r="K78" s="4">
         <v>0</v>
       </c>
-      <c r="L78" s="4">
-        <v>5</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N78" s="1"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="4"/>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L78" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M78" s="1"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="4"/>
+    </row>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C79" s="1">
         <v>1043</v>
       </c>
@@ -4039,20 +3821,17 @@
       <c r="K79" s="4">
         <v>0</v>
       </c>
-      <c r="L79" s="4">
-        <v>5</v>
-      </c>
-      <c r="M79" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="O79" s="2"/>
-      <c r="P79" s="4"/>
-    </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="O80" s="2"/>
-      <c r="P80" s="4"/>
-    </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L79" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="4"/>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N80" s="2"/>
+      <c r="O80" s="4"/>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C81" s="1">
         <v>1044</v>
       </c>
@@ -4063,7 +3842,7 @@
         <v>4055</v>
       </c>
       <c r="F81" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G81" s="4">
         <v>50</v>
@@ -4080,16 +3859,13 @@
       <c r="K81" s="4">
         <v>0</v>
       </c>
-      <c r="L81" s="4">
-        <v>999</v>
-      </c>
-      <c r="M81" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O81" s="2"/>
-      <c r="P81" s="4"/>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L81" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="4"/>
+    </row>
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C82" s="1">
         <v>1045</v>
       </c>
@@ -4100,7 +3876,7 @@
         <v>61000041</v>
       </c>
       <c r="F82" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82" s="4">
         <v>50</v>
@@ -4117,16 +3893,13 @@
       <c r="K82" s="4">
         <v>0</v>
       </c>
-      <c r="L82" s="4">
-        <v>2</v>
-      </c>
-      <c r="M82" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="O82" s="2"/>
-      <c r="P82" s="4"/>
-    </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L82" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="4"/>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C83" s="1">
         <v>1046</v>
       </c>
@@ -4137,7 +3910,7 @@
         <v>61000042</v>
       </c>
       <c r="F83" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" s="4">
         <v>50</v>
@@ -4154,16 +3927,13 @@
       <c r="K83" s="4">
         <v>0</v>
       </c>
-      <c r="L83" s="4">
-        <v>2</v>
-      </c>
-      <c r="M83" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" s="4"/>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L83" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="4"/>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C84" s="1">
         <v>1047</v>
       </c>
@@ -4174,7 +3944,7 @@
         <v>61000043</v>
       </c>
       <c r="F84" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" s="4">
         <v>150</v>
@@ -4191,16 +3961,13 @@
       <c r="K84" s="4">
         <v>0</v>
       </c>
-      <c r="L84" s="4">
-        <v>2</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="O84" s="2"/>
-      <c r="P84" s="4"/>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L84" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="4"/>
+    </row>
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C85" s="1">
         <v>1048</v>
       </c>
@@ -4211,7 +3978,7 @@
         <v>61000044</v>
       </c>
       <c r="F85" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" s="4">
         <v>150</v>
@@ -4228,16 +3995,13 @@
       <c r="K85" s="4">
         <v>0</v>
       </c>
-      <c r="L85" s="4">
-        <v>2</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="O85" s="2"/>
-      <c r="P85" s="4"/>
-    </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L85" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="4"/>
+    </row>
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C86" s="1">
         <v>1049</v>
       </c>
@@ -4248,7 +4012,7 @@
         <v>61000045</v>
       </c>
       <c r="F86" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G86" s="4">
         <v>300</v>
@@ -4265,16 +4029,13 @@
       <c r="K86" s="4">
         <v>0</v>
       </c>
-      <c r="L86" s="4">
-        <v>2</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O86" s="2"/>
-      <c r="P86" s="4"/>
-    </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L86" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="4"/>
+    </row>
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C87" s="1">
         <v>1050</v>
       </c>
@@ -4285,7 +4046,7 @@
         <v>61000046</v>
       </c>
       <c r="F87" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" s="4">
         <v>300</v>
@@ -4302,16 +4063,13 @@
       <c r="K87" s="4">
         <v>0</v>
       </c>
-      <c r="L87" s="4">
-        <v>2</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O87" s="2"/>
-      <c r="P87" s="4"/>
-    </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L87" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="4"/>
+    </row>
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C88" s="1">
         <v>1051</v>
       </c>
@@ -4322,7 +4080,7 @@
         <v>61000047</v>
       </c>
       <c r="F88" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" s="4">
         <v>400</v>
@@ -4339,16 +4097,13 @@
       <c r="K88" s="4">
         <v>0</v>
       </c>
-      <c r="L88" s="4">
-        <v>2</v>
-      </c>
-      <c r="M88" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="O88" s="2"/>
-      <c r="P88" s="4"/>
-    </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="L88" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="4"/>
+    </row>
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C89" s="1">
         <v>1052</v>
       </c>
@@ -4359,7 +4114,7 @@
         <v>61000048</v>
       </c>
       <c r="F89" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" s="4">
         <v>400</v>
@@ -4376,102 +4131,99 @@
       <c r="K89" s="4">
         <v>0</v>
       </c>
-      <c r="L89" s="4">
-        <v>2</v>
-      </c>
-      <c r="M89" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="O89" s="2"/>
-      <c r="P89" s="4"/>
-    </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="O90" s="2"/>
-      <c r="P90" s="4"/>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="O91" s="2"/>
-      <c r="P91" s="4"/>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="O92" s="2"/>
-      <c r="P92" s="4"/>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="O93" s="2"/>
-      <c r="P93" s="4"/>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="O94" s="2"/>
-      <c r="P94" s="4"/>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="O95" s="2"/>
-      <c r="P95" s="4"/>
-    </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="O96" s="2"/>
-      <c r="P96" s="4"/>
-    </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O97" s="2"/>
-      <c r="P97" s="4"/>
-    </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O98" s="2"/>
-      <c r="P98" s="4"/>
-    </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O99" s="2"/>
-      <c r="P99" s="4"/>
-    </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O100" s="2"/>
-      <c r="P100" s="4"/>
-    </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O101" s="2"/>
-      <c r="P101" s="4"/>
-    </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O102" s="2"/>
-      <c r="P102" s="4"/>
-    </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O103" s="2"/>
-      <c r="P103" s="4"/>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O104" s="2"/>
-      <c r="P104" s="4"/>
-    </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O105" s="2"/>
-      <c r="P105" s="4"/>
-    </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O106" s="2"/>
-      <c r="P106" s="4"/>
-    </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O107" s="2"/>
-      <c r="P107" s="4"/>
-    </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O108" s="2"/>
-      <c r="P108" s="4"/>
-    </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O109" s="2"/>
-      <c r="P109" s="4"/>
-    </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="15:16">
-      <c r="O110" s="2"/>
-      <c r="P110" s="4"/>
+      <c r="L89" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="4"/>
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N90" s="2"/>
+      <c r="O90" s="4"/>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N91" s="2"/>
+      <c r="O91" s="4"/>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N92" s="2"/>
+      <c r="O92" s="4"/>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N93" s="2"/>
+      <c r="O93" s="4"/>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N94" s="2"/>
+      <c r="O94" s="4"/>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N95" s="2"/>
+      <c r="O95" s="4"/>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N96" s="2"/>
+      <c r="O96" s="4"/>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N97" s="2"/>
+      <c r="O97" s="4"/>
+    </row>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N98" s="2"/>
+      <c r="O98" s="4"/>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N99" s="2"/>
+      <c r="O99" s="4"/>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N100" s="2"/>
+      <c r="O100" s="4"/>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N101" s="2"/>
+      <c r="O101" s="4"/>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N102" s="2"/>
+      <c r="O102" s="4"/>
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N103" s="2"/>
+      <c r="O103" s="4"/>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N104" s="2"/>
+      <c r="O104" s="4"/>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N105" s="2"/>
+      <c r="O105" s="4"/>
+    </row>
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N106" s="2"/>
+      <c r="O106" s="4"/>
+    </row>
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N107" s="2"/>
+      <c r="O107" s="4"/>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N108" s="2"/>
+      <c r="O108" s="4"/>
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N109" s="2"/>
+      <c r="O109" s="4"/>
+    </row>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="14:15">
+      <c r="N110" s="2"/>
+      <c r="O110" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="99">
   <si>
     <t>#</t>
   </si>
@@ -334,6 +334,33 @@
   </si>
   <si>
     <t>极青战靴</t>
+  </si>
+  <si>
+    <t>极虎精粹</t>
+  </si>
+  <si>
+    <t>极虎神剑</t>
+  </si>
+  <si>
+    <t>极虎神甲</t>
+  </si>
+  <si>
+    <t>极虎面罩</t>
+  </si>
+  <si>
+    <t>极虎项链</t>
+  </si>
+  <si>
+    <t>极虎护腕</t>
+  </si>
+  <si>
+    <t>极虎护戒</t>
+  </si>
+  <si>
+    <t>极虎腰带</t>
+  </si>
+  <si>
+    <t>极虎战靴</t>
   </si>
 </sst>
 </file>
@@ -4142,82 +4169,352 @@
       <c r="O90" s="4"/>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C91" s="1">
+        <v>1053</v>
+      </c>
+      <c r="D91" s="1">
+        <v>7</v>
+      </c>
+      <c r="E91" s="4">
+        <v>4056</v>
+      </c>
+      <c r="F91" s="4">
+        <v>150</v>
+      </c>
+      <c r="G91" s="4">
+        <v>50</v>
+      </c>
+      <c r="H91" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I91" s="4">
+        <v>10</v>
+      </c>
+      <c r="J91" s="4">
+        <v>0</v>
+      </c>
+      <c r="K91" s="4">
+        <v>0</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="N91" s="2"/>
       <c r="O91" s="4"/>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C92" s="1">
+        <v>1054</v>
+      </c>
+      <c r="D92" s="1">
+        <v>7</v>
+      </c>
+      <c r="E92" s="4">
+        <v>61000049</v>
+      </c>
+      <c r="F92" s="4">
+        <v>1</v>
+      </c>
+      <c r="G92" s="4">
+        <v>50</v>
+      </c>
+      <c r="H92" s="4">
+        <v>400</v>
+      </c>
+      <c r="I92" s="4">
+        <v>10</v>
+      </c>
+      <c r="J92" s="4">
+        <v>0</v>
+      </c>
+      <c r="K92" s="4">
+        <v>0</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="N92" s="2"/>
       <c r="O92" s="4"/>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C93" s="1">
+        <v>1055</v>
+      </c>
+      <c r="D93" s="1">
+        <v>7</v>
+      </c>
+      <c r="E93" s="4">
+        <v>61000050</v>
+      </c>
+      <c r="F93" s="4">
+        <v>1</v>
+      </c>
+      <c r="G93" s="4">
+        <v>50</v>
+      </c>
+      <c r="H93" s="4">
+        <v>400</v>
+      </c>
+      <c r="I93" s="4">
+        <v>10</v>
+      </c>
+      <c r="J93" s="4">
+        <v>0</v>
+      </c>
+      <c r="K93" s="4">
+        <v>0</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="N93" s="2"/>
       <c r="O93" s="4"/>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C94" s="1">
+        <v>1056</v>
+      </c>
+      <c r="D94" s="1">
+        <v>7</v>
+      </c>
+      <c r="E94" s="4">
+        <v>61000051</v>
+      </c>
+      <c r="F94" s="4">
+        <v>1</v>
+      </c>
+      <c r="G94" s="4">
+        <v>150</v>
+      </c>
+      <c r="H94" s="4">
+        <v>450</v>
+      </c>
+      <c r="I94" s="4">
+        <v>10</v>
+      </c>
+      <c r="J94" s="4">
+        <v>0</v>
+      </c>
+      <c r="K94" s="4">
+        <v>0</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="N94" s="2"/>
       <c r="O94" s="4"/>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C95" s="1">
+        <v>1057</v>
+      </c>
+      <c r="D95" s="1">
+        <v>7</v>
+      </c>
+      <c r="E95" s="4">
+        <v>61000052</v>
+      </c>
+      <c r="F95" s="4">
+        <v>1</v>
+      </c>
+      <c r="G95" s="4">
+        <v>150</v>
+      </c>
+      <c r="H95" s="4">
+        <v>450</v>
+      </c>
+      <c r="I95" s="4">
+        <v>10</v>
+      </c>
+      <c r="J95" s="4">
+        <v>0</v>
+      </c>
+      <c r="K95" s="4">
+        <v>0</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="N95" s="2"/>
       <c r="O95" s="4"/>
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C96" s="1">
+        <v>1058</v>
+      </c>
+      <c r="D96" s="1">
+        <v>7</v>
+      </c>
+      <c r="E96" s="4">
+        <v>61000053</v>
+      </c>
+      <c r="F96" s="4">
+        <v>1</v>
+      </c>
+      <c r="G96" s="4">
+        <v>300</v>
+      </c>
+      <c r="H96" s="4">
+        <v>650</v>
+      </c>
+      <c r="I96" s="4">
+        <v>10</v>
+      </c>
+      <c r="J96" s="4">
+        <v>0</v>
+      </c>
+      <c r="K96" s="4">
+        <v>0</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="4"/>
     </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C97" s="1">
+        <v>1059</v>
+      </c>
+      <c r="D97" s="1">
+        <v>7</v>
+      </c>
+      <c r="E97" s="4">
+        <v>61000054</v>
+      </c>
+      <c r="F97" s="4">
+        <v>1</v>
+      </c>
+      <c r="G97" s="4">
+        <v>300</v>
+      </c>
+      <c r="H97" s="4">
+        <v>650</v>
+      </c>
+      <c r="I97" s="4">
+        <v>10</v>
+      </c>
+      <c r="J97" s="4">
+        <v>0</v>
+      </c>
+      <c r="K97" s="4">
+        <v>0</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="N97" s="2"/>
       <c r="O97" s="4"/>
     </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C98" s="1">
+        <v>1060</v>
+      </c>
+      <c r="D98" s="1">
+        <v>7</v>
+      </c>
+      <c r="E98" s="4">
+        <v>61000055</v>
+      </c>
+      <c r="F98" s="4">
+        <v>1</v>
+      </c>
+      <c r="G98" s="4">
+        <v>400</v>
+      </c>
+      <c r="H98" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I98" s="4">
+        <v>10</v>
+      </c>
+      <c r="J98" s="4">
+        <v>0</v>
+      </c>
+      <c r="K98" s="4">
+        <v>0</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="N98" s="2"/>
       <c r="O98" s="4"/>
     </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C99" s="1">
+        <v>1061</v>
+      </c>
+      <c r="D99" s="1">
+        <v>7</v>
+      </c>
+      <c r="E99" s="4">
+        <v>61000056</v>
+      </c>
+      <c r="F99" s="4">
+        <v>1</v>
+      </c>
+      <c r="G99" s="4">
+        <v>400</v>
+      </c>
+      <c r="H99" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I99" s="4">
+        <v>10</v>
+      </c>
+      <c r="J99" s="4">
+        <v>0</v>
+      </c>
+      <c r="K99" s="4">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="N99" s="2"/>
       <c r="O99" s="4"/>
     </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N100" s="2"/>
       <c r="O100" s="4"/>
     </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N101" s="2"/>
       <c r="O101" s="4"/>
     </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N102" s="2"/>
       <c r="O102" s="4"/>
     </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N103" s="2"/>
       <c r="O103" s="4"/>
     </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N104" s="2"/>
       <c r="O104" s="4"/>
     </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N105" s="2"/>
       <c r="O105" s="4"/>
     </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N106" s="2"/>
       <c r="O106" s="4"/>
     </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N107" s="2"/>
       <c r="O107" s="4"/>
     </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N108" s="2"/>
       <c r="O108" s="4"/>
     </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N109" s="2"/>
       <c r="O109" s="4"/>
     </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="14:15">
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="N110" s="2"/>
       <c r="O110" s="4"/>
     </row>

--- a/Excel/WorldDropConfig.xlsx
+++ b/Excel/WorldDropConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -64,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -361,6 +366,33 @@
   </si>
   <si>
     <t>极虎战靴</t>
+  </si>
+  <si>
+    <t>极雀精粹</t>
+  </si>
+  <si>
+    <t>极雀神剑</t>
+  </si>
+  <si>
+    <t>极雀神甲</t>
+  </si>
+  <si>
+    <t>极雀面罩</t>
+  </si>
+  <si>
+    <t>极雀项链</t>
+  </si>
+  <si>
+    <t>极雀护腕</t>
+  </si>
+  <si>
+    <t>极雀护戒</t>
+  </si>
+  <si>
+    <t>极雀腰带</t>
+  </si>
+  <si>
+    <t>极雀战靴</t>
   </si>
 </sst>
 </file>
@@ -4479,38 +4511,308 @@
       <c r="O100" s="4"/>
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C101" s="1">
+        <v>1062</v>
+      </c>
+      <c r="D101" s="1">
+        <v>8</v>
+      </c>
+      <c r="E101" s="4">
+        <v>4057</v>
+      </c>
+      <c r="F101" s="4">
+        <v>150</v>
+      </c>
+      <c r="G101" s="4">
+        <v>50</v>
+      </c>
+      <c r="H101" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I101" s="4">
+        <v>10</v>
+      </c>
+      <c r="J101" s="4">
+        <v>0</v>
+      </c>
+      <c r="K101" s="4">
+        <v>0</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" s="4"/>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C102" s="1">
+        <v>1063</v>
+      </c>
+      <c r="D102" s="1">
+        <v>8</v>
+      </c>
+      <c r="E102" s="4">
+        <v>61000057</v>
+      </c>
+      <c r="F102" s="4">
+        <v>1</v>
+      </c>
+      <c r="G102" s="4">
+        <v>50</v>
+      </c>
+      <c r="H102" s="4">
+        <v>400</v>
+      </c>
+      <c r="I102" s="4">
+        <v>10</v>
+      </c>
+      <c r="J102" s="4">
+        <v>0</v>
+      </c>
+      <c r="K102" s="4">
+        <v>0</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" s="4"/>
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C103" s="1">
+        <v>1064</v>
+      </c>
+      <c r="D103" s="1">
+        <v>8</v>
+      </c>
+      <c r="E103" s="4">
+        <v>61000058</v>
+      </c>
+      <c r="F103" s="4">
+        <v>1</v>
+      </c>
+      <c r="G103" s="4">
+        <v>50</v>
+      </c>
+      <c r="H103" s="4">
+        <v>400</v>
+      </c>
+      <c r="I103" s="4">
+        <v>10</v>
+      </c>
+      <c r="J103" s="4">
+        <v>0</v>
+      </c>
+      <c r="K103" s="4">
+        <v>0</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="N103" s="2"/>
       <c r="O103" s="4"/>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C104" s="1">
+        <v>1065</v>
+      </c>
+      <c r="D104" s="1">
+        <v>8</v>
+      </c>
+      <c r="E104" s="4">
+        <v>61000059</v>
+      </c>
+      <c r="F104" s="4">
+        <v>1</v>
+      </c>
+      <c r="G104" s="4">
+        <v>150</v>
+      </c>
+      <c r="H104" s="4">
+        <v>450</v>
+      </c>
+      <c r="I104" s="4">
+        <v>10</v>
+      </c>
+      <c r="J104" s="4">
+        <v>0</v>
+      </c>
+      <c r="K104" s="4">
+        <v>0</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="N104" s="2"/>
       <c r="O104" s="4"/>
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C105" s="1">
+        <v>1066</v>
+      </c>
+      <c r="D105" s="1">
+        <v>8</v>
+      </c>
+      <c r="E105" s="4">
+        <v>61000060</v>
+      </c>
+      <c r="F105" s="4">
+        <v>1</v>
+      </c>
+      <c r="G105" s="4">
+        <v>150</v>
+      </c>
+      <c r="H105" s="4">
+        <v>450</v>
+      </c>
+      <c r="I105" s="4">
+        <v>10</v>
+      </c>
+      <c r="J105" s="4">
+        <v>0</v>
+      </c>
+      <c r="K105" s="4">
+        <v>0</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="N105" s="2"/>
       <c r="O105" s="4"/>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C106" s="1">
+        <v>1067</v>
+      </c>
+      <c r="D106" s="1">
+        <v>8</v>
+      </c>
+      <c r="E106" s="4">
+        <v>61000061</v>
+      </c>
+      <c r="F106" s="4">
+        <v>1</v>
+      </c>
+      <c r="G106" s="4">
+        <v>300</v>
+      </c>
+      <c r="H106" s="4">
+        <v>650</v>
+      </c>
+      <c r="I106" s="4">
+        <v>10</v>
+      </c>
+      <c r="J106" s="4">
+        <v>0</v>
+      </c>
+      <c r="K106" s="4">
+        <v>0</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="N106" s="2"/>
       <c r="O106" s="4"/>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C107" s="1">
+        <v>1068</v>
+      </c>
+      <c r="D107" s="1">
+        <v>8</v>
+      </c>
+      <c r="E107" s="4">
+        <v>61000062</v>
+      </c>
+      <c r="F107" s="4">
+        <v>1</v>
+      </c>
+      <c r="G107" s="4">
+        <v>300</v>
+      </c>
+      <c r="H107" s="4">
+        <v>650</v>
+      </c>
+      <c r="I107" s="4">
+        <v>10</v>
+      </c>
+      <c r="J107" s="4">
+        <v>0</v>
+      </c>
+      <c r="K107" s="4">
+        <v>0</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="N107" s="2"/>
       <c r="O107" s="4"/>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C108" s="1">
+        <v>1069</v>
+      </c>
+      <c r="D108" s="1">
+        <v>8</v>
+      </c>
+      <c r="E108" s="4">
+        <v>61000063</v>
+      </c>
+      <c r="F108" s="4">
+        <v>1</v>
+      </c>
+      <c r="G108" s="4">
+        <v>400</v>
+      </c>
+      <c r="H108" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I108" s="4">
+        <v>10</v>
+      </c>
+      <c r="J108" s="4">
+        <v>0</v>
+      </c>
+      <c r="K108" s="4">
+        <v>0</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="N108" s="2"/>
       <c r="O108" s="4"/>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C109" s="1">
+        <v>1070</v>
+      </c>
+      <c r="D109" s="1">
+        <v>8</v>
+      </c>
+      <c r="E109" s="4">
+        <v>61000064</v>
+      </c>
+      <c r="F109" s="4">
+        <v>1</v>
+      </c>
+      <c r="G109" s="4">
+        <v>400</v>
+      </c>
+      <c r="H109" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I109" s="4">
+        <v>10</v>
+      </c>
+      <c r="J109" s="4">
+        <v>0</v>
+      </c>
+      <c r="K109" s="4">
+        <v>0</v>
+      </c>
+      <c r="L109" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="N109" s="2"/>
       <c r="O109" s="4"/>
     </row>
